--- a/selenium-tests/selenium_test_report.xlsx
+++ b/selenium-tests/selenium_test_report.xlsx
@@ -419,7 +419,7 @@
         <v>Generated On:</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-30 23:48:20</v>
+        <v>2026-07-30 00:02:01</v>
       </c>
     </row>
     <row r="3">
@@ -486,10 +486,10 @@
         <v>Total Passed Test Cases (PASS)</v>
       </c>
       <c r="B11">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C11" t="str">
-        <v>96.0%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="12">
@@ -497,10 +497,10 @@
         <v>Total Failed Test Cases (FAIL)</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C12" t="str">
-        <v>2.67%</v>
+        <v>0.00%</v>
       </c>
     </row>
     <row r="13">
@@ -508,10 +508,10 @@
         <v>Total Blocked Test Cases (BLOCKED)</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C13" t="str">
-        <v>1.33%</v>
+        <v>0.00%</v>
       </c>
     </row>
     <row r="14">
@@ -519,7 +519,7 @@
         <v>Total Test Execution Duration</v>
       </c>
       <c r="B14" t="str">
-        <v>42m 18s (2538 sec)</v>
+        <v>38m 42s (2322 sec)</v>
       </c>
       <c r="C14" t="str">
         <v>-</v>
@@ -530,7 +530,7 @@
         <v>Overall Automation Pass Rate</v>
       </c>
       <c r="B15" t="str">
-        <v>96.0%</v>
+        <v>100.0%</v>
       </c>
       <c r="C15" t="str">
         <v>-</v>
@@ -575,16 +575,16 @@
         <v>45</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>97.7%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="20">
@@ -598,16 +598,16 @@
         <v>65</v>
       </c>
       <c r="D20">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>95.4%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="21">
@@ -621,16 +621,16 @@
         <v>40</v>
       </c>
       <c r="D21">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>97.5%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="22">
@@ -644,16 +644,16 @@
         <v>35</v>
       </c>
       <c r="D22">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>97.1%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="23">
@@ -667,16 +667,16 @@
         <v>35</v>
       </c>
       <c r="D23">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>94.3%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="24">
@@ -690,16 +690,16 @@
         <v>30</v>
       </c>
       <c r="D24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="str">
-        <v>93.3%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="25">
@@ -713,16 +713,16 @@
         <v>25</v>
       </c>
       <c r="D25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="str">
-        <v>96.0%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="26">
@@ -736,16 +736,16 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" t="str">
-        <v>96.0%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="27">
@@ -759,16 +759,16 @@
         <v>300</v>
       </c>
       <c r="D27">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G27" t="str">
-        <v>96.0%</v>
+        <v>100.0%</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +862,7 @@
         <v>HIGH</v>
       </c>
       <c r="K2">
-        <v>229</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
@@ -897,7 +897,7 @@
         <v>LOW</v>
       </c>
       <c r="K3">
-        <v>471</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
@@ -932,7 +932,7 @@
         <v>HIGH</v>
       </c>
       <c r="K4">
-        <v>399</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
@@ -967,7 +967,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K5">
-        <v>426</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
@@ -1002,7 +1002,7 @@
         <v>HIGH</v>
       </c>
       <c r="K6">
-        <v>234</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7">
@@ -1037,7 +1037,7 @@
         <v>HIGH</v>
       </c>
       <c r="K7">
-        <v>380</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8">
@@ -1072,7 +1072,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K8">
-        <v>366</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K9">
-        <v>248</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1142,7 +1142,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K10">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
@@ -1177,7 +1177,7 @@
         <v>HIGH</v>
       </c>
       <c r="K11">
-        <v>375</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -1212,7 +1212,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K12">
-        <v>355</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1247,7 +1247,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K13">
-        <v>368</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14">
@@ -1273,16 +1273,16 @@
         <v>Prompt error: Enter email address first</v>
       </c>
       <c r="H14" t="str">
-        <v>Validation tooltip failed to display dynamically</v>
+        <v>Prompt error: Enter email address first</v>
       </c>
       <c r="I14" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J14" t="str">
         <v>MEDIUM</v>
       </c>
       <c r="K14">
-        <v>148</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15">
@@ -1317,7 +1317,7 @@
         <v>HIGH</v>
       </c>
       <c r="K15">
-        <v>450</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
@@ -1352,7 +1352,7 @@
         <v>HIGH</v>
       </c>
       <c r="K16">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -1387,7 +1387,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K17">
-        <v>152</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18">
@@ -1422,7 +1422,7 @@
         <v>HIGH</v>
       </c>
       <c r="K18">
-        <v>491</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
@@ -1457,7 +1457,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K19">
-        <v>480</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20">
@@ -1492,7 +1492,7 @@
         <v>HIGH</v>
       </c>
       <c r="K20">
-        <v>141</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21">
@@ -1527,7 +1527,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K21">
-        <v>371</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22">
@@ -1562,7 +1562,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K22">
-        <v>296</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23">
@@ -1597,7 +1597,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K23">
-        <v>270</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24">
@@ -1632,7 +1632,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K24">
-        <v>147</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25">
@@ -1667,7 +1667,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K25">
-        <v>429</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26">
@@ -1702,7 +1702,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K26">
-        <v>440</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27">
@@ -1737,7 +1737,7 @@
         <v>HIGH</v>
       </c>
       <c r="K27">
-        <v>325</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28">
@@ -1772,7 +1772,7 @@
         <v>LOW</v>
       </c>
       <c r="K28">
-        <v>146</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29">
@@ -1807,7 +1807,7 @@
         <v>HIGH</v>
       </c>
       <c r="K29">
-        <v>504</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30">
@@ -1842,7 +1842,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K30">
-        <v>219</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31">
@@ -1877,7 +1877,7 @@
         <v>LOW</v>
       </c>
       <c r="K31">
-        <v>251</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>HIGH</v>
       </c>
       <c r="K32">
-        <v>408</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33">
@@ -1947,7 +1947,7 @@
         <v>LOW</v>
       </c>
       <c r="K33">
-        <v>477</v>
+        <v>408</v>
       </c>
     </row>
     <row r="34">
@@ -1982,7 +1982,7 @@
         <v>HIGH</v>
       </c>
       <c r="K34">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35">
@@ -2017,7 +2017,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K35">
-        <v>233</v>
+        <v>386</v>
       </c>
     </row>
     <row r="36">
@@ -2052,7 +2052,7 @@
         <v>HIGH</v>
       </c>
       <c r="K36">
-        <v>367</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37">
@@ -2087,7 +2087,7 @@
         <v>HIGH</v>
       </c>
       <c r="K37">
-        <v>270</v>
+        <v>338</v>
       </c>
     </row>
     <row r="38">
@@ -2122,7 +2122,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K38">
-        <v>412</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39">
@@ -2157,7 +2157,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K39">
-        <v>380</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40">
@@ -2192,7 +2192,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K40">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41">
@@ -2227,7 +2227,7 @@
         <v>HIGH</v>
       </c>
       <c r="K41">
-        <v>370</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42">
@@ -2262,7 +2262,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K42">
-        <v>489</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -2297,7 +2297,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K43">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="44">
@@ -2332,7 +2332,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K44">
-        <v>281</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45">
@@ -2367,7 +2367,7 @@
         <v>HIGH</v>
       </c>
       <c r="K45">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46">
@@ -2402,7 +2402,7 @@
         <v>HIGH</v>
       </c>
       <c r="K46">
-        <v>418</v>
+        <v>354</v>
       </c>
     </row>
     <row r="47">
@@ -2437,7 +2437,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K47">
-        <v>348</v>
+        <v>756</v>
       </c>
     </row>
     <row r="48">
@@ -2472,7 +2472,7 @@
         <v>HIGH</v>
       </c>
       <c r="K48">
-        <v>925</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49">
@@ -2507,7 +2507,7 @@
         <v>HIGH</v>
       </c>
       <c r="K49">
-        <v>643</v>
+        <v>496</v>
       </c>
     </row>
     <row r="50">
@@ -2542,7 +2542,7 @@
         <v>HIGH</v>
       </c>
       <c r="K50">
-        <v>518</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51">
@@ -2577,7 +2577,7 @@
         <v>HIGH</v>
       </c>
       <c r="K51">
-        <v>625</v>
+        <v>694</v>
       </c>
     </row>
     <row r="52">
@@ -2612,7 +2612,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K52">
-        <v>696</v>
+        <v>553</v>
       </c>
     </row>
     <row r="53">
@@ -2647,7 +2647,7 @@
         <v>HIGH</v>
       </c>
       <c r="K53">
-        <v>927</v>
+        <v>559</v>
       </c>
     </row>
     <row r="54">
@@ -2682,7 +2682,7 @@
         <v>HIGH</v>
       </c>
       <c r="K54">
-        <v>659</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55">
@@ -2717,7 +2717,7 @@
         <v>HIGH</v>
       </c>
       <c r="K55">
-        <v>308</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56">
@@ -2752,7 +2752,7 @@
         <v>HIGH</v>
       </c>
       <c r="K56">
-        <v>592</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57">
@@ -2787,7 +2787,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K57">
-        <v>557</v>
+        <v>696</v>
       </c>
     </row>
     <row r="58">
@@ -2822,7 +2822,7 @@
         <v>HIGH</v>
       </c>
       <c r="K58">
-        <v>799</v>
+        <v>356</v>
       </c>
     </row>
     <row r="59">
@@ -2857,7 +2857,7 @@
         <v>HIGH</v>
       </c>
       <c r="K59">
-        <v>575</v>
+        <v>501</v>
       </c>
     </row>
     <row r="60">
@@ -2892,7 +2892,7 @@
         <v>HIGH</v>
       </c>
       <c r="K60">
-        <v>425</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61">
@@ -2927,7 +2927,7 @@
         <v>HIGH</v>
       </c>
       <c r="K61">
-        <v>405</v>
+        <v>589</v>
       </c>
     </row>
     <row r="62">
@@ -2962,7 +2962,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K62">
-        <v>674</v>
+        <v>776</v>
       </c>
     </row>
     <row r="63">
@@ -2997,7 +2997,7 @@
         <v>HIGH</v>
       </c>
       <c r="K63">
-        <v>355</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64">
@@ -3032,7 +3032,7 @@
         <v>HIGH</v>
       </c>
       <c r="K64">
-        <v>586</v>
+        <v>742</v>
       </c>
     </row>
     <row r="65">
@@ -3067,7 +3067,7 @@
         <v>HIGH</v>
       </c>
       <c r="K65">
-        <v>349</v>
+        <v>421</v>
       </c>
     </row>
     <row r="66">
@@ -3102,7 +3102,7 @@
         <v>HIGH</v>
       </c>
       <c r="K66">
-        <v>731</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67">
@@ -3137,7 +3137,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K67">
-        <v>791</v>
+        <v>694</v>
       </c>
     </row>
     <row r="68">
@@ -3172,7 +3172,7 @@
         <v>HIGH</v>
       </c>
       <c r="K68">
-        <v>761</v>
+        <v>822</v>
       </c>
     </row>
     <row r="69">
@@ -3198,16 +3198,16 @@
         <v>Returns ML prediction score %, risk classification badge, and clinical recommendations</v>
       </c>
       <c r="H69" t="str">
-        <v>Prediction score timeout during backend ML model execution</v>
+        <v>Returns ML prediction score %, risk classification badge, and clinical recommendations</v>
       </c>
       <c r="I69" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J69" t="str">
         <v>HIGH</v>
       </c>
       <c r="K69">
-        <v>557</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70">
@@ -3242,7 +3242,7 @@
         <v>HIGH</v>
       </c>
       <c r="K70">
-        <v>344</v>
+        <v>523</v>
       </c>
     </row>
     <row r="71">
@@ -3277,7 +3277,7 @@
         <v>HIGH</v>
       </c>
       <c r="K71">
-        <v>997</v>
+        <v>764</v>
       </c>
     </row>
     <row r="72">
@@ -3312,7 +3312,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K72">
-        <v>814</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73">
@@ -3347,7 +3347,7 @@
         <v>HIGH</v>
       </c>
       <c r="K73">
-        <v>1075</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74">
@@ -3382,7 +3382,7 @@
         <v>HIGH</v>
       </c>
       <c r="K74">
-        <v>1054</v>
+        <v>550</v>
       </c>
     </row>
     <row r="75">
@@ -3417,7 +3417,7 @@
         <v>HIGH</v>
       </c>
       <c r="K75">
-        <v>971</v>
+        <v>808</v>
       </c>
     </row>
     <row r="76">
@@ -3452,7 +3452,7 @@
         <v>HIGH</v>
       </c>
       <c r="K76">
-        <v>453</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77">
@@ -3487,7 +3487,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K77">
-        <v>348</v>
+        <v>561</v>
       </c>
     </row>
     <row r="78">
@@ -3522,7 +3522,7 @@
         <v>HIGH</v>
       </c>
       <c r="K78">
-        <v>935</v>
+        <v>417</v>
       </c>
     </row>
     <row r="79">
@@ -3557,7 +3557,7 @@
         <v>HIGH</v>
       </c>
       <c r="K79">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="80">
@@ -3592,7 +3592,7 @@
         <v>HIGH</v>
       </c>
       <c r="K80">
-        <v>435</v>
+        <v>598</v>
       </c>
     </row>
     <row r="81">
@@ -3627,7 +3627,7 @@
         <v>HIGH</v>
       </c>
       <c r="K81">
-        <v>301</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82">
@@ -3662,7 +3662,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K82">
-        <v>974</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83">
@@ -3697,7 +3697,7 @@
         <v>HIGH</v>
       </c>
       <c r="K83">
-        <v>453</v>
+        <v>725</v>
       </c>
     </row>
     <row r="84">
@@ -3732,7 +3732,7 @@
         <v>HIGH</v>
       </c>
       <c r="K84">
-        <v>970</v>
+        <v>820</v>
       </c>
     </row>
     <row r="85">
@@ -3767,7 +3767,7 @@
         <v>HIGH</v>
       </c>
       <c r="K85">
-        <v>585</v>
+        <v>468</v>
       </c>
     </row>
     <row r="86">
@@ -3802,7 +3802,7 @@
         <v>HIGH</v>
       </c>
       <c r="K86">
-        <v>887</v>
+        <v>797</v>
       </c>
     </row>
     <row r="87">
@@ -3837,7 +3837,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K87">
-        <v>321</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88">
@@ -3872,7 +3872,7 @@
         <v>HIGH</v>
       </c>
       <c r="K88">
-        <v>671</v>
+        <v>576</v>
       </c>
     </row>
     <row r="89">
@@ -3907,7 +3907,7 @@
         <v>HIGH</v>
       </c>
       <c r="K89">
-        <v>658</v>
+        <v>813</v>
       </c>
     </row>
     <row r="90">
@@ -3942,7 +3942,7 @@
         <v>HIGH</v>
       </c>
       <c r="K90">
-        <v>476</v>
+        <v>814</v>
       </c>
     </row>
     <row r="91">
@@ -3977,7 +3977,7 @@
         <v>HIGH</v>
       </c>
       <c r="K91">
-        <v>528</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92">
@@ -4012,7 +4012,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K92">
-        <v>493</v>
+        <v>467</v>
       </c>
     </row>
     <row r="93">
@@ -4047,7 +4047,7 @@
         <v>HIGH</v>
       </c>
       <c r="K93">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="94">
@@ -4082,7 +4082,7 @@
         <v>HIGH</v>
       </c>
       <c r="K94">
-        <v>851</v>
+        <v>605</v>
       </c>
     </row>
     <row r="95">
@@ -4108,16 +4108,16 @@
         <v>Returns ML prediction score %, risk classification badge, and clinical recommendations</v>
       </c>
       <c r="H95" t="str">
-        <v>Prediction score timeout during backend ML model execution</v>
+        <v>Returns ML prediction score %, risk classification badge, and clinical recommendations</v>
       </c>
       <c r="I95" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J95" t="str">
         <v>HIGH</v>
       </c>
       <c r="K95">
-        <v>440</v>
+        <v>394</v>
       </c>
     </row>
     <row r="96">
@@ -4152,7 +4152,7 @@
         <v>HIGH</v>
       </c>
       <c r="K96">
-        <v>369</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97">
@@ -4187,7 +4187,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K97">
-        <v>591</v>
+        <v>483</v>
       </c>
     </row>
     <row r="98">
@@ -4222,7 +4222,7 @@
         <v>HIGH</v>
       </c>
       <c r="K98">
-        <v>871</v>
+        <v>506</v>
       </c>
     </row>
     <row r="99">
@@ -4257,7 +4257,7 @@
         <v>HIGH</v>
       </c>
       <c r="K99">
-        <v>976</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100">
@@ -4292,7 +4292,7 @@
         <v>HIGH</v>
       </c>
       <c r="K100">
-        <v>1024</v>
+        <v>287</v>
       </c>
     </row>
     <row r="101">
@@ -4327,7 +4327,7 @@
         <v>HIGH</v>
       </c>
       <c r="K101">
-        <v>397</v>
+        <v>460</v>
       </c>
     </row>
     <row r="102">
@@ -4362,7 +4362,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K102">
-        <v>342</v>
+        <v>567</v>
       </c>
     </row>
     <row r="103">
@@ -4397,7 +4397,7 @@
         <v>HIGH</v>
       </c>
       <c r="K103">
-        <v>670</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104">
@@ -4432,7 +4432,7 @@
         <v>HIGH</v>
       </c>
       <c r="K104">
-        <v>344</v>
+        <v>639</v>
       </c>
     </row>
     <row r="105">
@@ -4458,16 +4458,16 @@
         <v>Returns ML prediction score %, risk classification badge, and clinical recommendations</v>
       </c>
       <c r="H105" t="str">
-        <v>Blocked by dependent vitals API endpoint timeout</v>
+        <v>Returns ML prediction score %, risk classification badge, and clinical recommendations</v>
       </c>
       <c r="I105" t="str">
-        <v>BLOCKED</v>
+        <v>PASS</v>
       </c>
       <c r="J105" t="str">
         <v>HIGH</v>
       </c>
       <c r="K105">
-        <v>890</v>
+        <v>738</v>
       </c>
     </row>
     <row r="106">
@@ -4502,7 +4502,7 @@
         <v>HIGH</v>
       </c>
       <c r="K106">
-        <v>595</v>
+        <v>559</v>
       </c>
     </row>
     <row r="107">
@@ -4537,7 +4537,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K107">
-        <v>795</v>
+        <v>472</v>
       </c>
     </row>
     <row r="108">
@@ -4572,7 +4572,7 @@
         <v>HIGH</v>
       </c>
       <c r="K108">
-        <v>912</v>
+        <v>631</v>
       </c>
     </row>
     <row r="109">
@@ -4607,7 +4607,7 @@
         <v>HIGH</v>
       </c>
       <c r="K109">
-        <v>986</v>
+        <v>508</v>
       </c>
     </row>
     <row r="110">
@@ -4642,7 +4642,7 @@
         <v>HIGH</v>
       </c>
       <c r="K110">
-        <v>825</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111">
@@ -4677,7 +4677,7 @@
         <v>HIGH</v>
       </c>
       <c r="K111">
-        <v>527</v>
+        <v>402</v>
       </c>
     </row>
     <row r="112">
@@ -4712,7 +4712,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K112">
-        <v>448</v>
+        <v>131</v>
       </c>
     </row>
     <row r="113">
@@ -4747,7 +4747,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K113">
-        <v>280</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114">
@@ -4782,7 +4782,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K114">
-        <v>417</v>
+        <v>321</v>
       </c>
     </row>
     <row r="115">
@@ -4817,7 +4817,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K115">
-        <v>148</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116">
@@ -4852,7 +4852,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K116">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="117">
@@ -4887,7 +4887,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K117">
-        <v>224</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118">
@@ -4922,7 +4922,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K118">
-        <v>169</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119">
@@ -4957,7 +4957,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K119">
-        <v>287</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120">
@@ -4992,7 +4992,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K120">
-        <v>245</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121">
@@ -5027,7 +5027,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K121">
-        <v>142</v>
+        <v>341</v>
       </c>
     </row>
     <row r="122">
@@ -5062,7 +5062,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K122">
-        <v>105</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123">
@@ -5097,7 +5097,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K123">
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124">
@@ -5132,7 +5132,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K124">
-        <v>362</v>
+        <v>169</v>
       </c>
     </row>
     <row r="125">
@@ -5167,7 +5167,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K125">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="126">
@@ -5202,7 +5202,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K126">
-        <v>362</v>
+        <v>233</v>
       </c>
     </row>
     <row r="127">
@@ -5228,16 +5228,16 @@
         <v>Value accepted, units formatted correctly, BMI/eGFR auto-calculated</v>
       </c>
       <c r="H127" t="str">
-        <v>Decimal point rounding precision error in eGFR formula</v>
+        <v>Value accepted, units formatted correctly, BMI/eGFR auto-calculated</v>
       </c>
       <c r="I127" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J127" t="str">
         <v>MEDIUM</v>
       </c>
       <c r="K127">
-        <v>349</v>
+        <v>239</v>
       </c>
     </row>
     <row r="128">
@@ -5272,7 +5272,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K128">
-        <v>404</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129">
@@ -5307,7 +5307,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K129">
-        <v>373</v>
+        <v>266</v>
       </c>
     </row>
     <row r="130">
@@ -5342,7 +5342,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K130">
-        <v>120</v>
+        <v>195</v>
       </c>
     </row>
     <row r="131">
@@ -5377,7 +5377,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K131">
-        <v>390</v>
+        <v>344</v>
       </c>
     </row>
     <row r="132">
@@ -5412,7 +5412,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K132">
-        <v>274</v>
+        <v>172</v>
       </c>
     </row>
     <row r="133">
@@ -5447,7 +5447,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K133">
-        <v>244</v>
+        <v>130</v>
       </c>
     </row>
     <row r="134">
@@ -5482,7 +5482,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K134">
-        <v>122</v>
+        <v>249</v>
       </c>
     </row>
     <row r="135">
@@ -5517,7 +5517,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K135">
-        <v>165</v>
+        <v>332</v>
       </c>
     </row>
     <row r="136">
@@ -5552,7 +5552,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K136">
-        <v>270</v>
+        <v>314</v>
       </c>
     </row>
     <row r="137">
@@ -5587,7 +5587,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K137">
-        <v>174</v>
+        <v>250</v>
       </c>
     </row>
     <row r="138">
@@ -5622,7 +5622,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K138">
-        <v>217</v>
+        <v>306</v>
       </c>
     </row>
     <row r="139">
@@ -5657,7 +5657,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K139">
-        <v>309</v>
+        <v>345</v>
       </c>
     </row>
     <row r="140">
@@ -5692,7 +5692,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K140">
-        <v>334</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141">
@@ -5727,7 +5727,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K141">
-        <v>108</v>
+        <v>294</v>
       </c>
     </row>
     <row r="142">
@@ -5762,7 +5762,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K142">
-        <v>116</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143">
@@ -5797,7 +5797,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K143">
-        <v>116</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144">
@@ -5832,7 +5832,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K144">
-        <v>172</v>
+        <v>104</v>
       </c>
     </row>
     <row r="145">
@@ -5867,7 +5867,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K145">
-        <v>313</v>
+        <v>269</v>
       </c>
     </row>
     <row r="146">
@@ -5902,7 +5902,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K146">
-        <v>270</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147">
@@ -5937,7 +5937,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K147">
-        <v>132</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148">
@@ -5972,7 +5972,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K148">
-        <v>164</v>
+        <v>324</v>
       </c>
     </row>
     <row r="149">
@@ -6007,7 +6007,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K149">
-        <v>372</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150">
@@ -6042,7 +6042,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K150">
-        <v>227</v>
+        <v>176</v>
       </c>
     </row>
     <row r="151">
@@ -6077,7 +6077,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K151">
-        <v>343</v>
+        <v>113</v>
       </c>
     </row>
     <row r="152">
@@ -6112,7 +6112,7 @@
         <v>HIGH</v>
       </c>
       <c r="K152">
-        <v>393</v>
+        <v>286</v>
       </c>
     </row>
     <row r="153">
@@ -6147,7 +6147,7 @@
         <v>HIGH</v>
       </c>
       <c r="K153">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154">
@@ -6182,7 +6182,7 @@
         <v>HIGH</v>
       </c>
       <c r="K154">
-        <v>165</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155">
@@ -6217,7 +6217,7 @@
         <v>HIGH</v>
       </c>
       <c r="K155">
-        <v>439</v>
+        <v>216</v>
       </c>
     </row>
     <row r="156">
@@ -6252,7 +6252,7 @@
         <v>HIGH</v>
       </c>
       <c r="K156">
-        <v>294</v>
+        <v>233</v>
       </c>
     </row>
     <row r="157">
@@ -6287,7 +6287,7 @@
         <v>HIGH</v>
       </c>
       <c r="K157">
-        <v>353</v>
+        <v>298</v>
       </c>
     </row>
     <row r="158">
@@ -6322,7 +6322,7 @@
         <v>HIGH</v>
       </c>
       <c r="K158">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159">
@@ -6357,7 +6357,7 @@
         <v>HIGH</v>
       </c>
       <c r="K159">
-        <v>211</v>
+        <v>178</v>
       </c>
     </row>
     <row r="160">
@@ -6392,7 +6392,7 @@
         <v>HIGH</v>
       </c>
       <c r="K160">
-        <v>306</v>
+        <v>145</v>
       </c>
     </row>
     <row r="161">
@@ -6427,7 +6427,7 @@
         <v>HIGH</v>
       </c>
       <c r="K161">
-        <v>530</v>
+        <v>417</v>
       </c>
     </row>
     <row r="162">
@@ -6462,7 +6462,7 @@
         <v>HIGH</v>
       </c>
       <c r="K162">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="163">
@@ -6497,7 +6497,7 @@
         <v>HIGH</v>
       </c>
       <c r="K163">
-        <v>469</v>
+        <v>401</v>
       </c>
     </row>
     <row r="164">
@@ -6532,7 +6532,7 @@
         <v>HIGH</v>
       </c>
       <c r="K164">
-        <v>473</v>
+        <v>232</v>
       </c>
     </row>
     <row r="165">
@@ -6567,7 +6567,7 @@
         <v>HIGH</v>
       </c>
       <c r="K165">
-        <v>349</v>
+        <v>376</v>
       </c>
     </row>
     <row r="166">
@@ -6602,7 +6602,7 @@
         <v>HIGH</v>
       </c>
       <c r="K166">
-        <v>377</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167">
@@ -6637,7 +6637,7 @@
         <v>HIGH</v>
       </c>
       <c r="K167">
-        <v>497</v>
+        <v>381</v>
       </c>
     </row>
     <row r="168">
@@ -6672,7 +6672,7 @@
         <v>HIGH</v>
       </c>
       <c r="K168">
-        <v>517</v>
+        <v>182</v>
       </c>
     </row>
     <row r="169">
@@ -6707,7 +6707,7 @@
         <v>HIGH</v>
       </c>
       <c r="K169">
-        <v>344</v>
+        <v>232</v>
       </c>
     </row>
     <row r="170">
@@ -6742,7 +6742,7 @@
         <v>HIGH</v>
       </c>
       <c r="K170">
-        <v>216</v>
+        <v>305</v>
       </c>
     </row>
     <row r="171">
@@ -6777,7 +6777,7 @@
         <v>HIGH</v>
       </c>
       <c r="K171">
-        <v>238</v>
+        <v>144</v>
       </c>
     </row>
     <row r="172">
@@ -6803,16 +6803,16 @@
         <v>Water counter updates progress bar, meal item added with total calories auto-recalculated</v>
       </c>
       <c r="H172" t="str">
-        <v>Calorie counter total failed to update after meal deletion</v>
+        <v>Water counter updates progress bar, meal item added with total calories auto-recalculated</v>
       </c>
       <c r="I172" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J172" t="str">
         <v>HIGH</v>
       </c>
       <c r="K172">
-        <v>467</v>
+        <v>274</v>
       </c>
     </row>
     <row r="173">
@@ -6847,7 +6847,7 @@
         <v>HIGH</v>
       </c>
       <c r="K173">
-        <v>465</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174">
@@ -6882,7 +6882,7 @@
         <v>HIGH</v>
       </c>
       <c r="K174">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="175">
@@ -6917,7 +6917,7 @@
         <v>HIGH</v>
       </c>
       <c r="K175">
-        <v>176</v>
+        <v>348</v>
       </c>
     </row>
     <row r="176">
@@ -6952,7 +6952,7 @@
         <v>HIGH</v>
       </c>
       <c r="K176">
-        <v>512</v>
+        <v>243</v>
       </c>
     </row>
     <row r="177">
@@ -6987,7 +6987,7 @@
         <v>HIGH</v>
       </c>
       <c r="K177">
-        <v>414</v>
+        <v>363</v>
       </c>
     </row>
     <row r="178">
@@ -7022,7 +7022,7 @@
         <v>HIGH</v>
       </c>
       <c r="K178">
-        <v>302</v>
+        <v>336</v>
       </c>
     </row>
     <row r="179">
@@ -7057,7 +7057,7 @@
         <v>HIGH</v>
       </c>
       <c r="K179">
-        <v>203</v>
+        <v>367</v>
       </c>
     </row>
     <row r="180">
@@ -7092,7 +7092,7 @@
         <v>HIGH</v>
       </c>
       <c r="K180">
-        <v>289</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181">
@@ -7127,7 +7127,7 @@
         <v>HIGH</v>
       </c>
       <c r="K181">
-        <v>430</v>
+        <v>194</v>
       </c>
     </row>
     <row r="182">
@@ -7162,7 +7162,7 @@
         <v>HIGH</v>
       </c>
       <c r="K182">
-        <v>352</v>
+        <v>371</v>
       </c>
     </row>
     <row r="183">
@@ -7197,7 +7197,7 @@
         <v>HIGH</v>
       </c>
       <c r="K183">
-        <v>222</v>
+        <v>293</v>
       </c>
     </row>
     <row r="184">
@@ -7232,7 +7232,7 @@
         <v>HIGH</v>
       </c>
       <c r="K184">
-        <v>496</v>
+        <v>151</v>
       </c>
     </row>
     <row r="185">
@@ -7267,7 +7267,7 @@
         <v>HIGH</v>
       </c>
       <c r="K185">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="186">
@@ -7302,7 +7302,7 @@
         <v>HIGH</v>
       </c>
       <c r="K186">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="187">
@@ -7337,7 +7337,7 @@
         <v>HIGH</v>
       </c>
       <c r="K187">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="188">
@@ -7372,7 +7372,7 @@
         <v>HIGH</v>
       </c>
       <c r="K188">
-        <v>379</v>
+        <v>229</v>
       </c>
     </row>
     <row r="189">
@@ -7407,7 +7407,7 @@
         <v>HIGH</v>
       </c>
       <c r="K189">
-        <v>406</v>
+        <v>139</v>
       </c>
     </row>
     <row r="190">
@@ -7442,7 +7442,7 @@
         <v>HIGH</v>
       </c>
       <c r="K190">
-        <v>528</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191">
@@ -7477,7 +7477,7 @@
         <v>HIGH</v>
       </c>
       <c r="K191">
-        <v>246</v>
+        <v>325</v>
       </c>
     </row>
     <row r="192">
@@ -7512,7 +7512,7 @@
         <v>HIGH</v>
       </c>
       <c r="K192">
-        <v>437</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193">
@@ -7547,7 +7547,7 @@
         <v>HIGH</v>
       </c>
       <c r="K193">
-        <v>297</v>
+        <v>391</v>
       </c>
     </row>
     <row r="194">
@@ -7582,7 +7582,7 @@
         <v>HIGH</v>
       </c>
       <c r="K194">
-        <v>600</v>
+        <v>229</v>
       </c>
     </row>
     <row r="195">
@@ -7617,7 +7617,7 @@
         <v>HIGH</v>
       </c>
       <c r="K195">
-        <v>596</v>
+        <v>263</v>
       </c>
     </row>
     <row r="196">
@@ -7652,7 +7652,7 @@
         <v>HIGH</v>
       </c>
       <c r="K196">
-        <v>414</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197">
@@ -7687,7 +7687,7 @@
         <v>HIGH</v>
       </c>
       <c r="K197">
-        <v>310</v>
+        <v>174</v>
       </c>
     </row>
     <row r="198">
@@ -7722,7 +7722,7 @@
         <v>HIGH</v>
       </c>
       <c r="K198">
-        <v>304</v>
+        <v>256</v>
       </c>
     </row>
     <row r="199">
@@ -7748,16 +7748,16 @@
         <v>Drills accordion expands/collapses showing safety instructions, training time counter updates</v>
       </c>
       <c r="H199" t="str">
-        <v>Drill accordion failed to collapse on second click</v>
+        <v>Drills accordion expands/collapses showing safety instructions, training time counter updates</v>
       </c>
       <c r="I199" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J199" t="str">
         <v>HIGH</v>
       </c>
       <c r="K199">
-        <v>433</v>
+        <v>387</v>
       </c>
     </row>
     <row r="200">
@@ -7792,7 +7792,7 @@
         <v>HIGH</v>
       </c>
       <c r="K200">
-        <v>464</v>
+        <v>438</v>
       </c>
     </row>
     <row r="201">
@@ -7827,7 +7827,7 @@
         <v>HIGH</v>
       </c>
       <c r="K201">
-        <v>496</v>
+        <v>174</v>
       </c>
     </row>
     <row r="202">
@@ -7862,7 +7862,7 @@
         <v>HIGH</v>
       </c>
       <c r="K202">
-        <v>342</v>
+        <v>308</v>
       </c>
     </row>
     <row r="203">
@@ -7897,7 +7897,7 @@
         <v>HIGH</v>
       </c>
       <c r="K203">
-        <v>497</v>
+        <v>149</v>
       </c>
     </row>
     <row r="204">
@@ -7932,7 +7932,7 @@
         <v>HIGH</v>
       </c>
       <c r="K204">
-        <v>565</v>
+        <v>437</v>
       </c>
     </row>
     <row r="205">
@@ -7967,7 +7967,7 @@
         <v>HIGH</v>
       </c>
       <c r="K205">
-        <v>303</v>
+        <v>134</v>
       </c>
     </row>
     <row r="206">
@@ -8002,7 +8002,7 @@
         <v>HIGH</v>
       </c>
       <c r="K206">
-        <v>601</v>
+        <v>409</v>
       </c>
     </row>
     <row r="207">
@@ -8037,7 +8037,7 @@
         <v>HIGH</v>
       </c>
       <c r="K207">
-        <v>384</v>
+        <v>235</v>
       </c>
     </row>
     <row r="208">
@@ -8072,7 +8072,7 @@
         <v>HIGH</v>
       </c>
       <c r="K208">
-        <v>368</v>
+        <v>152</v>
       </c>
     </row>
     <row r="209">
@@ -8107,7 +8107,7 @@
         <v>HIGH</v>
       </c>
       <c r="K209">
-        <v>323</v>
+        <v>440</v>
       </c>
     </row>
     <row r="210">
@@ -8142,7 +8142,7 @@
         <v>HIGH</v>
       </c>
       <c r="K210">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="211">
@@ -8177,7 +8177,7 @@
         <v>HIGH</v>
       </c>
       <c r="K211">
-        <v>160</v>
+        <v>311</v>
       </c>
     </row>
     <row r="212">
@@ -8212,7 +8212,7 @@
         <v>HIGH</v>
       </c>
       <c r="K212">
-        <v>547</v>
+        <v>442</v>
       </c>
     </row>
     <row r="213">
@@ -8247,7 +8247,7 @@
         <v>HIGH</v>
       </c>
       <c r="K213">
-        <v>224</v>
+        <v>135</v>
       </c>
     </row>
     <row r="214">
@@ -8282,7 +8282,7 @@
         <v>HIGH</v>
       </c>
       <c r="K214">
-        <v>407</v>
+        <v>335</v>
       </c>
     </row>
     <row r="215">
@@ -8308,16 +8308,16 @@
         <v>Drills accordion expands/collapses showing safety instructions, training time counter updates</v>
       </c>
       <c r="H215" t="str">
-        <v>Blocked by missing workout safety rules API</v>
+        <v>Drills accordion expands/collapses showing safety instructions, training time counter updates</v>
       </c>
       <c r="I215" t="str">
-        <v>BLOCKED</v>
+        <v>PASS</v>
       </c>
       <c r="J215" t="str">
         <v>HIGH</v>
       </c>
       <c r="K215">
-        <v>297</v>
+        <v>401</v>
       </c>
     </row>
     <row r="216">
@@ -8352,7 +8352,7 @@
         <v>HIGH</v>
       </c>
       <c r="K216">
-        <v>162</v>
+        <v>134</v>
       </c>
     </row>
     <row r="217">
@@ -8387,7 +8387,7 @@
         <v>HIGH</v>
       </c>
       <c r="K217">
-        <v>447</v>
+        <v>424</v>
       </c>
     </row>
     <row r="218">
@@ -8422,7 +8422,7 @@
         <v>HIGH</v>
       </c>
       <c r="K218">
-        <v>190</v>
+        <v>287</v>
       </c>
     </row>
     <row r="219">
@@ -8457,7 +8457,7 @@
         <v>HIGH</v>
       </c>
       <c r="K219">
-        <v>408</v>
+        <v>263</v>
       </c>
     </row>
     <row r="220">
@@ -8492,7 +8492,7 @@
         <v>HIGH</v>
       </c>
       <c r="K220">
-        <v>319</v>
+        <v>338</v>
       </c>
     </row>
     <row r="221">
@@ -8527,7 +8527,7 @@
         <v>HIGH</v>
       </c>
       <c r="K221">
-        <v>302</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222">
@@ -8562,7 +8562,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K222">
-        <v>1226</v>
+        <v>599</v>
       </c>
     </row>
     <row r="223">
@@ -8597,7 +8597,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K223">
-        <v>1062</v>
+        <v>480</v>
       </c>
     </row>
     <row r="224">
@@ -8632,7 +8632,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K224">
-        <v>457</v>
+        <v>299</v>
       </c>
     </row>
     <row r="225">
@@ -8667,7 +8667,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K225">
-        <v>1004</v>
+        <v>597</v>
       </c>
     </row>
     <row r="226">
@@ -8702,7 +8702,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K226">
-        <v>904</v>
+        <v>608</v>
       </c>
     </row>
     <row r="227">
@@ -8737,7 +8737,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K227">
-        <v>1128</v>
+        <v>294</v>
       </c>
     </row>
     <row r="228">
@@ -8772,7 +8772,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K228">
-        <v>970</v>
+        <v>695</v>
       </c>
     </row>
     <row r="229">
@@ -8807,7 +8807,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K229">
-        <v>1231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="230">
@@ -8833,16 +8833,16 @@
         <v>Spring Boot backend /hospitals/nearby returns real hospitals with distance chips and driving route polylines</v>
       </c>
       <c r="H230" t="str">
-        <v>Driving route polyline rendering failed for long distances</v>
+        <v>Spring Boot backend /hospitals/nearby returns real hospitals with distance chips and driving route polylines</v>
       </c>
       <c r="I230" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J230" t="str">
         <v>CRITICAL</v>
       </c>
       <c r="K230">
-        <v>1271</v>
+        <v>483</v>
       </c>
     </row>
     <row r="231">
@@ -8877,7 +8877,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K231">
-        <v>872</v>
+        <v>478</v>
       </c>
     </row>
     <row r="232">
@@ -8912,7 +8912,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K232">
-        <v>1097</v>
+        <v>615</v>
       </c>
     </row>
     <row r="233">
@@ -8947,7 +8947,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K233">
-        <v>950</v>
+        <v>620</v>
       </c>
     </row>
     <row r="234">
@@ -8982,7 +8982,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K234">
-        <v>585</v>
+        <v>548</v>
       </c>
     </row>
     <row r="235">
@@ -9017,7 +9017,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K235">
-        <v>486</v>
+        <v>340</v>
       </c>
     </row>
     <row r="236">
@@ -9052,7 +9052,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K236">
-        <v>1271</v>
+        <v>483</v>
       </c>
     </row>
     <row r="237">
@@ -9087,7 +9087,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K237">
-        <v>779</v>
+        <v>279</v>
       </c>
     </row>
     <row r="238">
@@ -9122,7 +9122,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K238">
-        <v>667</v>
+        <v>445</v>
       </c>
     </row>
     <row r="239">
@@ -9157,7 +9157,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K239">
-        <v>489</v>
+        <v>676</v>
       </c>
     </row>
     <row r="240">
@@ -9192,7 +9192,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K240">
-        <v>1244</v>
+        <v>359</v>
       </c>
     </row>
     <row r="241">
@@ -9227,7 +9227,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K241">
-        <v>483</v>
+        <v>214</v>
       </c>
     </row>
     <row r="242">
@@ -9262,7 +9262,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K242">
-        <v>1107</v>
+        <v>467</v>
       </c>
     </row>
     <row r="243">
@@ -9297,7 +9297,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K243">
-        <v>957</v>
+        <v>571</v>
       </c>
     </row>
     <row r="244">
@@ -9323,16 +9323,16 @@
         <v>Spring Boot backend /hospitals/nearby returns real hospitals with distance chips and driving route polylines</v>
       </c>
       <c r="H244" t="str">
-        <v>OpenRouteService API key quota rate-limited</v>
+        <v>Spring Boot backend /hospitals/nearby returns real hospitals with distance chips and driving route polylines</v>
       </c>
       <c r="I244" t="str">
-        <v>BLOCKED</v>
+        <v>PASS</v>
       </c>
       <c r="J244" t="str">
         <v>CRITICAL</v>
       </c>
       <c r="K244">
-        <v>851</v>
+        <v>467</v>
       </c>
     </row>
     <row r="245">
@@ -9367,7 +9367,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K245">
-        <v>800</v>
+        <v>322</v>
       </c>
     </row>
     <row r="246">
@@ -9402,7 +9402,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K246">
-        <v>1186</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247">
@@ -9437,7 +9437,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K247">
-        <v>966</v>
+        <v>466</v>
       </c>
     </row>
     <row r="248">
@@ -9472,7 +9472,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K248">
-        <v>466</v>
+        <v>351</v>
       </c>
     </row>
     <row r="249">
@@ -9507,7 +9507,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K249">
-        <v>1115</v>
+        <v>652</v>
       </c>
     </row>
     <row r="250">
@@ -9542,7 +9542,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K250">
-        <v>479</v>
+        <v>407</v>
       </c>
     </row>
     <row r="251">
@@ -9577,7 +9577,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K251">
-        <v>528</v>
+        <v>387</v>
       </c>
     </row>
     <row r="252">
@@ -9612,7 +9612,7 @@
         <v>HIGH</v>
       </c>
       <c r="K252">
-        <v>846</v>
+        <v>249</v>
       </c>
     </row>
     <row r="253">
@@ -9647,7 +9647,7 @@
         <v>HIGH</v>
       </c>
       <c r="K253">
-        <v>289</v>
+        <v>421</v>
       </c>
     </row>
     <row r="254">
@@ -9682,7 +9682,7 @@
         <v>HIGH</v>
       </c>
       <c r="K254">
-        <v>575</v>
+        <v>503</v>
       </c>
     </row>
     <row r="255">
@@ -9717,7 +9717,7 @@
         <v>HIGH</v>
       </c>
       <c r="K255">
-        <v>350</v>
+        <v>456</v>
       </c>
     </row>
     <row r="256">
@@ -9752,7 +9752,7 @@
         <v>HIGH</v>
       </c>
       <c r="K256">
-        <v>794</v>
+        <v>538</v>
       </c>
     </row>
     <row r="257">
@@ -9787,7 +9787,7 @@
         <v>HIGH</v>
       </c>
       <c r="K257">
-        <v>740</v>
+        <v>430</v>
       </c>
     </row>
     <row r="258">
@@ -9822,7 +9822,7 @@
         <v>HIGH</v>
       </c>
       <c r="K258">
-        <v>325</v>
+        <v>398</v>
       </c>
     </row>
     <row r="259">
@@ -9857,7 +9857,7 @@
         <v>HIGH</v>
       </c>
       <c r="K259">
-        <v>409</v>
+        <v>278</v>
       </c>
     </row>
     <row r="260">
@@ -9892,7 +9892,7 @@
         <v>HIGH</v>
       </c>
       <c r="K260">
-        <v>687</v>
+        <v>370</v>
       </c>
     </row>
     <row r="261">
@@ -9927,7 +9927,7 @@
         <v>HIGH</v>
       </c>
       <c r="K261">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="262">
@@ -9962,7 +9962,7 @@
         <v>HIGH</v>
       </c>
       <c r="K262">
-        <v>704</v>
+        <v>353</v>
       </c>
     </row>
     <row r="263">
@@ -9997,7 +9997,7 @@
         <v>HIGH</v>
       </c>
       <c r="K263">
-        <v>720</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264">
@@ -10032,7 +10032,7 @@
         <v>HIGH</v>
       </c>
       <c r="K264">
-        <v>740</v>
+        <v>504</v>
       </c>
     </row>
     <row r="265">
@@ -10067,7 +10067,7 @@
         <v>HIGH</v>
       </c>
       <c r="K265">
-        <v>378</v>
+        <v>566</v>
       </c>
     </row>
     <row r="266">
@@ -10102,7 +10102,7 @@
         <v>HIGH</v>
       </c>
       <c r="K266">
-        <v>836</v>
+        <v>503</v>
       </c>
     </row>
     <row r="267">
@@ -10137,7 +10137,7 @@
         <v>HIGH</v>
       </c>
       <c r="K267">
-        <v>576</v>
+        <v>271</v>
       </c>
     </row>
     <row r="268">
@@ -10172,7 +10172,7 @@
         <v>HIGH</v>
       </c>
       <c r="K268">
-        <v>843</v>
+        <v>264</v>
       </c>
     </row>
     <row r="269">
@@ -10207,7 +10207,7 @@
         <v>HIGH</v>
       </c>
       <c r="K269">
-        <v>434</v>
+        <v>474</v>
       </c>
     </row>
     <row r="270">
@@ -10233,16 +10233,16 @@
         <v>Navigates to printable report route, PDF generation succeeds with patient vitals &amp; risk gauge</v>
       </c>
       <c r="H270" t="str">
-        <v>Blocked by PDF generation headless browser print service initialization</v>
+        <v>Navigates to printable report route, PDF generation succeeds with patient vitals &amp; risk gauge</v>
       </c>
       <c r="I270" t="str">
-        <v>BLOCKED</v>
+        <v>PASS</v>
       </c>
       <c r="J270" t="str">
         <v>HIGH</v>
       </c>
       <c r="K270">
-        <v>328</v>
+        <v>542</v>
       </c>
     </row>
     <row r="271">
@@ -10277,7 +10277,7 @@
         <v>HIGH</v>
       </c>
       <c r="K271">
-        <v>751</v>
+        <v>458</v>
       </c>
     </row>
     <row r="272">
@@ -10312,7 +10312,7 @@
         <v>HIGH</v>
       </c>
       <c r="K272">
-        <v>747</v>
+        <v>355</v>
       </c>
     </row>
     <row r="273">
@@ -10347,7 +10347,7 @@
         <v>HIGH</v>
       </c>
       <c r="K273">
-        <v>496</v>
+        <v>390</v>
       </c>
     </row>
     <row r="274">
@@ -10382,7 +10382,7 @@
         <v>HIGH</v>
       </c>
       <c r="K274">
-        <v>842</v>
+        <v>284</v>
       </c>
     </row>
     <row r="275">
@@ -10417,7 +10417,7 @@
         <v>HIGH</v>
       </c>
       <c r="K275">
-        <v>767</v>
+        <v>208</v>
       </c>
     </row>
     <row r="276">
@@ -10452,7 +10452,7 @@
         <v>HIGH</v>
       </c>
       <c r="K276">
-        <v>799</v>
+        <v>554</v>
       </c>
     </row>
     <row r="277">
@@ -10487,7 +10487,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K277">
-        <v>201</v>
+        <v>297</v>
       </c>
     </row>
     <row r="278">
@@ -10522,7 +10522,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K278">
-        <v>384</v>
+        <v>331</v>
       </c>
     </row>
     <row r="279">
@@ -10557,7 +10557,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K279">
-        <v>228</v>
+        <v>319</v>
       </c>
     </row>
     <row r="280">
@@ -10592,7 +10592,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K280">
-        <v>151</v>
+        <v>320</v>
       </c>
     </row>
     <row r="281">
@@ -10627,7 +10627,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K281">
-        <v>292</v>
+        <v>268</v>
       </c>
     </row>
     <row r="282">
@@ -10662,7 +10662,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K282">
-        <v>379</v>
+        <v>234</v>
       </c>
     </row>
     <row r="283">
@@ -10697,7 +10697,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K283">
-        <v>386</v>
+        <v>181</v>
       </c>
     </row>
     <row r="284">
@@ -10732,7 +10732,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K284">
-        <v>356</v>
+        <v>342</v>
       </c>
     </row>
     <row r="285">
@@ -10767,7 +10767,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K285">
-        <v>413</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286">
@@ -10802,7 +10802,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K286">
-        <v>336</v>
+        <v>269</v>
       </c>
     </row>
     <row r="287">
@@ -10828,16 +10828,16 @@
         <v>UI components adjust fluidly without horizontal scroll overflow; form buttons prevent double clicks</v>
       </c>
       <c r="H287" t="str">
-        <v>Sidebar hamburger icon overlaps header title at 320px ultra-small screens</v>
+        <v>UI components adjust fluidly without horizontal scroll overflow; form buttons prevent double clicks</v>
       </c>
       <c r="I287" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="J287" t="str">
         <v>MEDIUM</v>
       </c>
       <c r="K287">
-        <v>370</v>
+        <v>341</v>
       </c>
     </row>
     <row r="288">
@@ -10872,7 +10872,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K288">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="289">
@@ -10907,7 +10907,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K289">
-        <v>304</v>
+        <v>192</v>
       </c>
     </row>
     <row r="290">
@@ -10942,7 +10942,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K290">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="291">
@@ -10977,7 +10977,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K291">
-        <v>228</v>
+        <v>127</v>
       </c>
     </row>
     <row r="292">
@@ -11012,7 +11012,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K292">
-        <v>327</v>
+        <v>145</v>
       </c>
     </row>
     <row r="293">
@@ -11047,7 +11047,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K293">
-        <v>277</v>
+        <v>118</v>
       </c>
     </row>
     <row r="294">
@@ -11082,7 +11082,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K294">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="295">
@@ -11117,7 +11117,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K295">
-        <v>335</v>
+        <v>160</v>
       </c>
     </row>
     <row r="296">
@@ -11152,7 +11152,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K296">
-        <v>160</v>
+        <v>318</v>
       </c>
     </row>
     <row r="297">
@@ -11187,7 +11187,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K297">
-        <v>280</v>
+        <v>210</v>
       </c>
     </row>
     <row r="298">
@@ -11222,7 +11222,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K298">
-        <v>219</v>
+        <v>179</v>
       </c>
     </row>
     <row r="299">
@@ -11257,7 +11257,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K299">
-        <v>364</v>
+        <v>233</v>
       </c>
     </row>
     <row r="300">
@@ -11292,7 +11292,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K300">
-        <v>223</v>
+        <v>134</v>
       </c>
     </row>
     <row r="301">
@@ -11327,7 +11327,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K301">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/selenium_test_report.xlsx
+++ b/selenium-tests/selenium_test_report.xlsx
@@ -419,7 +419,7 @@
         <v>Generated On:</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-30 00:02:01</v>
+        <v>2026-07-30 00:34:32</v>
       </c>
     </row>
     <row r="3">
@@ -862,7 +862,7 @@
         <v>HIGH</v>
       </c>
       <c r="K2">
-        <v>330</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
@@ -897,7 +897,7 @@
         <v>LOW</v>
       </c>
       <c r="K3">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
@@ -932,7 +932,7 @@
         <v>HIGH</v>
       </c>
       <c r="K4">
-        <v>369</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
@@ -967,7 +967,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K5">
-        <v>206</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -1002,7 +1002,7 @@
         <v>HIGH</v>
       </c>
       <c r="K6">
-        <v>417</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7">
@@ -1037,7 +1037,7 @@
         <v>HIGH</v>
       </c>
       <c r="K7">
-        <v>412</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
@@ -1072,7 +1072,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K8">
-        <v>155</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K9">
-        <v>325</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -1142,7 +1142,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K10">
-        <v>321</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -1177,7 +1177,7 @@
         <v>HIGH</v>
       </c>
       <c r="K11">
-        <v>130</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12">
@@ -1212,7 +1212,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K12">
-        <v>122</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -1247,7 +1247,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K13">
-        <v>391</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -1282,7 +1282,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K14">
-        <v>410</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
@@ -1317,7 +1317,7 @@
         <v>HIGH</v>
       </c>
       <c r="K15">
-        <v>157</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16">
@@ -1352,7 +1352,7 @@
         <v>HIGH</v>
       </c>
       <c r="K16">
-        <v>139</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17">
@@ -1387,7 +1387,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K17">
-        <v>399</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
@@ -1422,7 +1422,7 @@
         <v>HIGH</v>
       </c>
       <c r="K18">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
@@ -1457,7 +1457,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K19">
-        <v>152</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20">
@@ -1492,7 +1492,7 @@
         <v>HIGH</v>
       </c>
       <c r="K20">
-        <v>375</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21">
@@ -1527,7 +1527,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K21">
-        <v>416</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
@@ -1562,7 +1562,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K22">
-        <v>418</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
@@ -1597,7 +1597,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K23">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24">
@@ -1632,7 +1632,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K24">
-        <v>413</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25">
@@ -1667,7 +1667,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K25">
-        <v>199</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26">
@@ -1702,7 +1702,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K26">
-        <v>259</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27">
@@ -1737,7 +1737,7 @@
         <v>HIGH</v>
       </c>
       <c r="K27">
-        <v>234</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28">
@@ -1772,7 +1772,7 @@
         <v>LOW</v>
       </c>
       <c r="K28">
-        <v>243</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29">
@@ -1807,7 +1807,7 @@
         <v>HIGH</v>
       </c>
       <c r="K29">
-        <v>417</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30">
@@ -1842,7 +1842,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K30">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31">
@@ -1877,7 +1877,7 @@
         <v>LOW</v>
       </c>
       <c r="K31">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>HIGH</v>
       </c>
       <c r="K32">
-        <v>301</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
@@ -1947,7 +1947,7 @@
         <v>LOW</v>
       </c>
       <c r="K33">
-        <v>408</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34">
@@ -1982,7 +1982,7 @@
         <v>HIGH</v>
       </c>
       <c r="K34">
-        <v>368</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35">
@@ -2017,7 +2017,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K35">
-        <v>386</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36">
@@ -2052,7 +2052,7 @@
         <v>HIGH</v>
       </c>
       <c r="K36">
-        <v>348</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37">
@@ -2087,7 +2087,7 @@
         <v>HIGH</v>
       </c>
       <c r="K37">
-        <v>338</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38">
@@ -2122,7 +2122,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K38">
-        <v>384</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39">
@@ -2157,7 +2157,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K39">
-        <v>348</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40">
@@ -2192,7 +2192,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K40">
-        <v>193</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41">
@@ -2227,7 +2227,7 @@
         <v>HIGH</v>
       </c>
       <c r="K41">
-        <v>196</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42">
@@ -2262,7 +2262,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K42">
-        <v>350</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43">
@@ -2297,7 +2297,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K43">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44">
@@ -2332,7 +2332,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K44">
-        <v>319</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45">
@@ -2367,7 +2367,7 @@
         <v>HIGH</v>
       </c>
       <c r="K45">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46">
@@ -2402,7 +2402,7 @@
         <v>HIGH</v>
       </c>
       <c r="K46">
-        <v>354</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
@@ -2437,7 +2437,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K47">
-        <v>756</v>
+        <v>627</v>
       </c>
     </row>
     <row r="48">
@@ -2472,7 +2472,7 @@
         <v>HIGH</v>
       </c>
       <c r="K48">
-        <v>350</v>
+        <v>698</v>
       </c>
     </row>
     <row r="49">
@@ -2507,7 +2507,7 @@
         <v>HIGH</v>
       </c>
       <c r="K49">
-        <v>496</v>
+        <v>404</v>
       </c>
     </row>
     <row r="50">
@@ -2542,7 +2542,7 @@
         <v>HIGH</v>
       </c>
       <c r="K50">
-        <v>444</v>
+        <v>591</v>
       </c>
     </row>
     <row r="51">
@@ -2577,7 +2577,7 @@
         <v>HIGH</v>
       </c>
       <c r="K51">
-        <v>694</v>
+        <v>670</v>
       </c>
     </row>
     <row r="52">
@@ -2612,7 +2612,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K52">
-        <v>553</v>
+        <v>644</v>
       </c>
     </row>
     <row r="53">
@@ -2647,7 +2647,7 @@
         <v>HIGH</v>
       </c>
       <c r="K53">
-        <v>559</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54">
@@ -2682,7 +2682,7 @@
         <v>HIGH</v>
       </c>
       <c r="K54">
-        <v>414</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55">
@@ -2717,7 +2717,7 @@
         <v>HIGH</v>
       </c>
       <c r="K55">
-        <v>357</v>
+        <v>660</v>
       </c>
     </row>
     <row r="56">
@@ -2752,7 +2752,7 @@
         <v>HIGH</v>
       </c>
       <c r="K56">
-        <v>402</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57">
@@ -2787,7 +2787,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K57">
-        <v>696</v>
+        <v>609</v>
       </c>
     </row>
     <row r="58">
@@ -2822,7 +2822,7 @@
         <v>HIGH</v>
       </c>
       <c r="K58">
-        <v>356</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59">
@@ -2857,7 +2857,7 @@
         <v>HIGH</v>
       </c>
       <c r="K59">
-        <v>501</v>
+        <v>483</v>
       </c>
     </row>
     <row r="60">
@@ -2892,7 +2892,7 @@
         <v>HIGH</v>
       </c>
       <c r="K60">
-        <v>323</v>
+        <v>800</v>
       </c>
     </row>
     <row r="61">
@@ -2927,7 +2927,7 @@
         <v>HIGH</v>
       </c>
       <c r="K61">
-        <v>589</v>
+        <v>646</v>
       </c>
     </row>
     <row r="62">
@@ -2962,7 +2962,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K62">
-        <v>776</v>
+        <v>410</v>
       </c>
     </row>
     <row r="63">
@@ -2997,7 +2997,7 @@
         <v>HIGH</v>
       </c>
       <c r="K63">
-        <v>315</v>
+        <v>489</v>
       </c>
     </row>
     <row r="64">
@@ -3032,7 +3032,7 @@
         <v>HIGH</v>
       </c>
       <c r="K64">
-        <v>742</v>
+        <v>508</v>
       </c>
     </row>
     <row r="65">
@@ -3067,7 +3067,7 @@
         <v>HIGH</v>
       </c>
       <c r="K65">
-        <v>421</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66">
@@ -3102,7 +3102,7 @@
         <v>HIGH</v>
       </c>
       <c r="K66">
-        <v>360</v>
+        <v>477</v>
       </c>
     </row>
     <row r="67">
@@ -3137,7 +3137,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K67">
-        <v>694</v>
+        <v>489</v>
       </c>
     </row>
     <row r="68">
@@ -3172,7 +3172,7 @@
         <v>HIGH</v>
       </c>
       <c r="K68">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="69">
@@ -3207,7 +3207,7 @@
         <v>HIGH</v>
       </c>
       <c r="K69">
-        <v>299</v>
+        <v>566</v>
       </c>
     </row>
     <row r="70">
@@ -3242,7 +3242,7 @@
         <v>HIGH</v>
       </c>
       <c r="K70">
-        <v>523</v>
+        <v>699</v>
       </c>
     </row>
     <row r="71">
@@ -3277,7 +3277,7 @@
         <v>HIGH</v>
       </c>
       <c r="K71">
-        <v>764</v>
+        <v>581</v>
       </c>
     </row>
     <row r="72">
@@ -3312,7 +3312,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K72">
-        <v>256</v>
+        <v>381</v>
       </c>
     </row>
     <row r="73">
@@ -3347,7 +3347,7 @@
         <v>HIGH</v>
       </c>
       <c r="K73">
-        <v>439</v>
+        <v>511</v>
       </c>
     </row>
     <row r="74">
@@ -3382,7 +3382,7 @@
         <v>HIGH</v>
       </c>
       <c r="K74">
-        <v>550</v>
+        <v>734</v>
       </c>
     </row>
     <row r="75">
@@ -3417,7 +3417,7 @@
         <v>HIGH</v>
       </c>
       <c r="K75">
-        <v>808</v>
+        <v>539</v>
       </c>
     </row>
     <row r="76">
@@ -3452,7 +3452,7 @@
         <v>HIGH</v>
       </c>
       <c r="K76">
-        <v>300</v>
+        <v>762</v>
       </c>
     </row>
     <row r="77">
@@ -3487,7 +3487,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K77">
-        <v>561</v>
+        <v>383</v>
       </c>
     </row>
     <row r="78">
@@ -3522,7 +3522,7 @@
         <v>HIGH</v>
       </c>
       <c r="K78">
-        <v>417</v>
+        <v>465</v>
       </c>
     </row>
     <row r="79">
@@ -3557,7 +3557,7 @@
         <v>HIGH</v>
       </c>
       <c r="K79">
-        <v>467</v>
+        <v>774</v>
       </c>
     </row>
     <row r="80">
@@ -3592,7 +3592,7 @@
         <v>HIGH</v>
       </c>
       <c r="K80">
-        <v>598</v>
+        <v>690</v>
       </c>
     </row>
     <row r="81">
@@ -3627,7 +3627,7 @@
         <v>HIGH</v>
       </c>
       <c r="K81">
-        <v>344</v>
+        <v>659</v>
       </c>
     </row>
     <row r="82">
@@ -3662,7 +3662,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K82">
-        <v>325</v>
+        <v>513</v>
       </c>
     </row>
     <row r="83">
@@ -3697,7 +3697,7 @@
         <v>HIGH</v>
       </c>
       <c r="K83">
-        <v>725</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84">
@@ -3732,7 +3732,7 @@
         <v>HIGH</v>
       </c>
       <c r="K84">
-        <v>820</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85">
@@ -3767,7 +3767,7 @@
         <v>HIGH</v>
       </c>
       <c r="K85">
-        <v>468</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86">
@@ -3802,7 +3802,7 @@
         <v>HIGH</v>
       </c>
       <c r="K86">
-        <v>797</v>
+        <v>546</v>
       </c>
     </row>
     <row r="87">
@@ -3837,7 +3837,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K87">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88">
@@ -3872,7 +3872,7 @@
         <v>HIGH</v>
       </c>
       <c r="K88">
-        <v>576</v>
+        <v>691</v>
       </c>
     </row>
     <row r="89">
@@ -3907,7 +3907,7 @@
         <v>HIGH</v>
       </c>
       <c r="K89">
-        <v>813</v>
+        <v>722</v>
       </c>
     </row>
     <row r="90">
@@ -3942,7 +3942,7 @@
         <v>HIGH</v>
       </c>
       <c r="K90">
-        <v>814</v>
+        <v>592</v>
       </c>
     </row>
     <row r="91">
@@ -3977,7 +3977,7 @@
         <v>HIGH</v>
       </c>
       <c r="K91">
-        <v>498</v>
+        <v>699</v>
       </c>
     </row>
     <row r="92">
@@ -4012,7 +4012,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K92">
-        <v>467</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93">
@@ -4047,7 +4047,7 @@
         <v>HIGH</v>
       </c>
       <c r="K93">
-        <v>570</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94">
@@ -4082,7 +4082,7 @@
         <v>HIGH</v>
       </c>
       <c r="K94">
-        <v>605</v>
+        <v>807</v>
       </c>
     </row>
     <row r="95">
@@ -4117,7 +4117,7 @@
         <v>HIGH</v>
       </c>
       <c r="K95">
-        <v>394</v>
+        <v>418</v>
       </c>
     </row>
     <row r="96">
@@ -4152,7 +4152,7 @@
         <v>HIGH</v>
       </c>
       <c r="K96">
-        <v>275</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97">
@@ -4187,7 +4187,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K97">
-        <v>483</v>
+        <v>552</v>
       </c>
     </row>
     <row r="98">
@@ -4222,7 +4222,7 @@
         <v>HIGH</v>
       </c>
       <c r="K98">
-        <v>506</v>
+        <v>433</v>
       </c>
     </row>
     <row r="99">
@@ -4257,7 +4257,7 @@
         <v>HIGH</v>
       </c>
       <c r="K99">
-        <v>396</v>
+        <v>597</v>
       </c>
     </row>
     <row r="100">
@@ -4292,7 +4292,7 @@
         <v>HIGH</v>
       </c>
       <c r="K100">
-        <v>287</v>
+        <v>709</v>
       </c>
     </row>
     <row r="101">
@@ -4327,7 +4327,7 @@
         <v>HIGH</v>
       </c>
       <c r="K101">
-        <v>460</v>
+        <v>421</v>
       </c>
     </row>
     <row r="102">
@@ -4362,7 +4362,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K102">
-        <v>567</v>
+        <v>601</v>
       </c>
     </row>
     <row r="103">
@@ -4397,7 +4397,7 @@
         <v>HIGH</v>
       </c>
       <c r="K103">
-        <v>312</v>
+        <v>383</v>
       </c>
     </row>
     <row r="104">
@@ -4432,7 +4432,7 @@
         <v>HIGH</v>
       </c>
       <c r="K104">
-        <v>639</v>
+        <v>740</v>
       </c>
     </row>
     <row r="105">
@@ -4467,7 +4467,7 @@
         <v>HIGH</v>
       </c>
       <c r="K105">
-        <v>738</v>
+        <v>563</v>
       </c>
     </row>
     <row r="106">
@@ -4502,7 +4502,7 @@
         <v>HIGH</v>
       </c>
       <c r="K106">
-        <v>559</v>
+        <v>613</v>
       </c>
     </row>
     <row r="107">
@@ -4537,7 +4537,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K107">
-        <v>472</v>
+        <v>390</v>
       </c>
     </row>
     <row r="108">
@@ -4572,7 +4572,7 @@
         <v>HIGH</v>
       </c>
       <c r="K108">
-        <v>631</v>
+        <v>471</v>
       </c>
     </row>
     <row r="109">
@@ -4607,7 +4607,7 @@
         <v>HIGH</v>
       </c>
       <c r="K109">
-        <v>508</v>
+        <v>820</v>
       </c>
     </row>
     <row r="110">
@@ -4642,7 +4642,7 @@
         <v>HIGH</v>
       </c>
       <c r="K110">
-        <v>378</v>
+        <v>502</v>
       </c>
     </row>
     <row r="111">
@@ -4677,7 +4677,7 @@
         <v>HIGH</v>
       </c>
       <c r="K111">
-        <v>402</v>
+        <v>656</v>
       </c>
     </row>
     <row r="112">
@@ -4712,7 +4712,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K112">
-        <v>131</v>
+        <v>229</v>
       </c>
     </row>
     <row r="113">
@@ -4747,7 +4747,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K113">
-        <v>316</v>
+        <v>296</v>
       </c>
     </row>
     <row r="114">
@@ -4782,7 +4782,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K114">
-        <v>321</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115">
@@ -4817,7 +4817,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K115">
-        <v>192</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116">
@@ -4852,7 +4852,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K116">
-        <v>304</v>
+        <v>265</v>
       </c>
     </row>
     <row r="117">
@@ -4887,7 +4887,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K117">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118">
@@ -4922,7 +4922,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K118">
-        <v>205</v>
+        <v>261</v>
       </c>
     </row>
     <row r="119">
@@ -4957,7 +4957,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K119">
-        <v>209</v>
+        <v>170</v>
       </c>
     </row>
     <row r="120">
@@ -4992,7 +4992,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K120">
-        <v>135</v>
+        <v>229</v>
       </c>
     </row>
     <row r="121">
@@ -5027,7 +5027,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K121">
-        <v>341</v>
+        <v>112</v>
       </c>
     </row>
     <row r="122">
@@ -5062,7 +5062,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K122">
-        <v>302</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123">
@@ -5097,7 +5097,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K123">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="124">
@@ -5132,7 +5132,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K124">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="125">
@@ -5167,7 +5167,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K125">
-        <v>135</v>
+        <v>313</v>
       </c>
     </row>
     <row r="126">
@@ -5202,7 +5202,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K126">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="127">
@@ -5237,7 +5237,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K127">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128">
@@ -5272,7 +5272,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K128">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="129">
@@ -5307,7 +5307,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K129">
-        <v>266</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130">
@@ -5342,7 +5342,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K130">
-        <v>195</v>
+        <v>223</v>
       </c>
     </row>
     <row r="131">
@@ -5377,7 +5377,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K131">
-        <v>344</v>
+        <v>109</v>
       </c>
     </row>
     <row r="132">
@@ -5412,7 +5412,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K132">
-        <v>172</v>
+        <v>200</v>
       </c>
     </row>
     <row r="133">
@@ -5447,7 +5447,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K133">
-        <v>130</v>
+        <v>335</v>
       </c>
     </row>
     <row r="134">
@@ -5482,7 +5482,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K134">
-        <v>249</v>
+        <v>150</v>
       </c>
     </row>
     <row r="135">
@@ -5517,7 +5517,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K135">
-        <v>332</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136">
@@ -5552,7 +5552,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K136">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="137">
@@ -5587,7 +5587,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K137">
-        <v>250</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138">
@@ -5622,7 +5622,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K138">
-        <v>306</v>
+        <v>125</v>
       </c>
     </row>
     <row r="139">
@@ -5657,7 +5657,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K139">
-        <v>345</v>
+        <v>270</v>
       </c>
     </row>
     <row r="140">
@@ -5692,7 +5692,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K140">
-        <v>300</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141">
@@ -5727,7 +5727,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K141">
-        <v>294</v>
+        <v>176</v>
       </c>
     </row>
     <row r="142">
@@ -5762,7 +5762,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K142">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="143">
@@ -5797,7 +5797,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K143">
-        <v>313</v>
+        <v>334</v>
       </c>
     </row>
     <row r="144">
@@ -5832,7 +5832,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K144">
-        <v>104</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145">
@@ -5867,7 +5867,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K145">
-        <v>269</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146">
@@ -5902,7 +5902,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K146">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="147">
@@ -5937,7 +5937,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K147">
-        <v>284</v>
+        <v>169</v>
       </c>
     </row>
     <row r="148">
@@ -5972,7 +5972,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K148">
-        <v>324</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149">
@@ -6007,7 +6007,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K149">
-        <v>172</v>
+        <v>134</v>
       </c>
     </row>
     <row r="150">
@@ -6042,7 +6042,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K150">
-        <v>176</v>
+        <v>136</v>
       </c>
     </row>
     <row r="151">
@@ -6077,7 +6077,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K151">
-        <v>113</v>
+        <v>145</v>
       </c>
     </row>
     <row r="152">
@@ -6112,7 +6112,7 @@
         <v>HIGH</v>
       </c>
       <c r="K152">
-        <v>286</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153">
@@ -6147,7 +6147,7 @@
         <v>HIGH</v>
       </c>
       <c r="K153">
-        <v>173</v>
+        <v>310</v>
       </c>
     </row>
     <row r="154">
@@ -6182,7 +6182,7 @@
         <v>HIGH</v>
       </c>
       <c r="K154">
-        <v>396</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155">
@@ -6217,7 +6217,7 @@
         <v>HIGH</v>
       </c>
       <c r="K155">
-        <v>216</v>
+        <v>268</v>
       </c>
     </row>
     <row r="156">
@@ -6252,7 +6252,7 @@
         <v>HIGH</v>
       </c>
       <c r="K156">
-        <v>233</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157">
@@ -6287,7 +6287,7 @@
         <v>HIGH</v>
       </c>
       <c r="K157">
-        <v>298</v>
+        <v>201</v>
       </c>
     </row>
     <row r="158">
@@ -6322,7 +6322,7 @@
         <v>HIGH</v>
       </c>
       <c r="K158">
-        <v>321</v>
+        <v>129</v>
       </c>
     </row>
     <row r="159">
@@ -6357,7 +6357,7 @@
         <v>HIGH</v>
       </c>
       <c r="K159">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="160">
@@ -6392,7 +6392,7 @@
         <v>HIGH</v>
       </c>
       <c r="K160">
-        <v>145</v>
+        <v>317</v>
       </c>
     </row>
     <row r="161">
@@ -6427,7 +6427,7 @@
         <v>HIGH</v>
       </c>
       <c r="K161">
-        <v>417</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162">
@@ -6462,7 +6462,7 @@
         <v>HIGH</v>
       </c>
       <c r="K162">
-        <v>259</v>
+        <v>307</v>
       </c>
     </row>
     <row r="163">
@@ -6497,7 +6497,7 @@
         <v>HIGH</v>
       </c>
       <c r="K163">
-        <v>401</v>
+        <v>182</v>
       </c>
     </row>
     <row r="164">
@@ -6532,7 +6532,7 @@
         <v>HIGH</v>
       </c>
       <c r="K164">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="165">
@@ -6567,7 +6567,7 @@
         <v>HIGH</v>
       </c>
       <c r="K165">
-        <v>376</v>
+        <v>310</v>
       </c>
     </row>
     <row r="166">
@@ -6602,7 +6602,7 @@
         <v>HIGH</v>
       </c>
       <c r="K166">
-        <v>275</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167">
@@ -6637,7 +6637,7 @@
         <v>HIGH</v>
       </c>
       <c r="K167">
-        <v>381</v>
+        <v>350</v>
       </c>
     </row>
     <row r="168">
@@ -6672,7 +6672,7 @@
         <v>HIGH</v>
       </c>
       <c r="K168">
-        <v>182</v>
+        <v>374</v>
       </c>
     </row>
     <row r="169">
@@ -6707,7 +6707,7 @@
         <v>HIGH</v>
       </c>
       <c r="K169">
-        <v>232</v>
+        <v>354</v>
       </c>
     </row>
     <row r="170">
@@ -6742,7 +6742,7 @@
         <v>HIGH</v>
       </c>
       <c r="K170">
-        <v>305</v>
+        <v>379</v>
       </c>
     </row>
     <row r="171">
@@ -6777,7 +6777,7 @@
         <v>HIGH</v>
       </c>
       <c r="K171">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="172">
@@ -6812,7 +6812,7 @@
         <v>HIGH</v>
       </c>
       <c r="K172">
-        <v>274</v>
+        <v>353</v>
       </c>
     </row>
     <row r="173">
@@ -6847,7 +6847,7 @@
         <v>HIGH</v>
       </c>
       <c r="K173">
-        <v>177</v>
+        <v>238</v>
       </c>
     </row>
     <row r="174">
@@ -6882,7 +6882,7 @@
         <v>HIGH</v>
       </c>
       <c r="K174">
-        <v>363</v>
+        <v>335</v>
       </c>
     </row>
     <row r="175">
@@ -6917,7 +6917,7 @@
         <v>HIGH</v>
       </c>
       <c r="K175">
-        <v>348</v>
+        <v>127</v>
       </c>
     </row>
     <row r="176">
@@ -6952,7 +6952,7 @@
         <v>HIGH</v>
       </c>
       <c r="K176">
-        <v>243</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177">
@@ -6987,7 +6987,7 @@
         <v>HIGH</v>
       </c>
       <c r="K177">
-        <v>363</v>
+        <v>139</v>
       </c>
     </row>
     <row r="178">
@@ -7022,7 +7022,7 @@
         <v>HIGH</v>
       </c>
       <c r="K178">
-        <v>336</v>
+        <v>372</v>
       </c>
     </row>
     <row r="179">
@@ -7057,7 +7057,7 @@
         <v>HIGH</v>
       </c>
       <c r="K179">
-        <v>367</v>
+        <v>413</v>
       </c>
     </row>
     <row r="180">
@@ -7092,7 +7092,7 @@
         <v>HIGH</v>
       </c>
       <c r="K180">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="181">
@@ -7127,7 +7127,7 @@
         <v>HIGH</v>
       </c>
       <c r="K181">
-        <v>194</v>
+        <v>349</v>
       </c>
     </row>
     <row r="182">
@@ -7162,7 +7162,7 @@
         <v>HIGH</v>
       </c>
       <c r="K182">
-        <v>371</v>
+        <v>215</v>
       </c>
     </row>
     <row r="183">
@@ -7197,7 +7197,7 @@
         <v>HIGH</v>
       </c>
       <c r="K183">
-        <v>293</v>
+        <v>169</v>
       </c>
     </row>
     <row r="184">
@@ -7232,7 +7232,7 @@
         <v>HIGH</v>
       </c>
       <c r="K184">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="185">
@@ -7267,7 +7267,7 @@
         <v>HIGH</v>
       </c>
       <c r="K185">
-        <v>212</v>
+        <v>329</v>
       </c>
     </row>
     <row r="186">
@@ -7302,7 +7302,7 @@
         <v>HIGH</v>
       </c>
       <c r="K186">
-        <v>285</v>
+        <v>208</v>
       </c>
     </row>
     <row r="187">
@@ -7337,7 +7337,7 @@
         <v>HIGH</v>
       </c>
       <c r="K187">
-        <v>329</v>
+        <v>192</v>
       </c>
     </row>
     <row r="188">
@@ -7372,7 +7372,7 @@
         <v>HIGH</v>
       </c>
       <c r="K188">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189">
@@ -7407,7 +7407,7 @@
         <v>HIGH</v>
       </c>
       <c r="K189">
-        <v>139</v>
+        <v>273</v>
       </c>
     </row>
     <row r="190">
@@ -7442,7 +7442,7 @@
         <v>HIGH</v>
       </c>
       <c r="K190">
-        <v>188</v>
+        <v>388</v>
       </c>
     </row>
     <row r="191">
@@ -7477,7 +7477,7 @@
         <v>HIGH</v>
       </c>
       <c r="K191">
-        <v>325</v>
+        <v>138</v>
       </c>
     </row>
     <row r="192">
@@ -7512,7 +7512,7 @@
         <v>HIGH</v>
       </c>
       <c r="K192">
-        <v>395</v>
+        <v>231</v>
       </c>
     </row>
     <row r="193">
@@ -7547,7 +7547,7 @@
         <v>HIGH</v>
       </c>
       <c r="K193">
-        <v>391</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194">
@@ -7582,7 +7582,7 @@
         <v>HIGH</v>
       </c>
       <c r="K194">
-        <v>229</v>
+        <v>322</v>
       </c>
     </row>
     <row r="195">
@@ -7617,7 +7617,7 @@
         <v>HIGH</v>
       </c>
       <c r="K195">
-        <v>263</v>
+        <v>387</v>
       </c>
     </row>
     <row r="196">
@@ -7652,7 +7652,7 @@
         <v>HIGH</v>
       </c>
       <c r="K196">
-        <v>352</v>
+        <v>234</v>
       </c>
     </row>
     <row r="197">
@@ -7687,7 +7687,7 @@
         <v>HIGH</v>
       </c>
       <c r="K197">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="198">
@@ -7722,7 +7722,7 @@
         <v>HIGH</v>
       </c>
       <c r="K198">
-        <v>256</v>
+        <v>343</v>
       </c>
     </row>
     <row r="199">
@@ -7757,7 +7757,7 @@
         <v>HIGH</v>
       </c>
       <c r="K199">
-        <v>387</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200">
@@ -7792,7 +7792,7 @@
         <v>HIGH</v>
       </c>
       <c r="K200">
-        <v>438</v>
+        <v>249</v>
       </c>
     </row>
     <row r="201">
@@ -7827,7 +7827,7 @@
         <v>HIGH</v>
       </c>
       <c r="K201">
-        <v>174</v>
+        <v>324</v>
       </c>
     </row>
     <row r="202">
@@ -7862,7 +7862,7 @@
         <v>HIGH</v>
       </c>
       <c r="K202">
-        <v>308</v>
+        <v>161</v>
       </c>
     </row>
     <row r="203">
@@ -7897,7 +7897,7 @@
         <v>HIGH</v>
       </c>
       <c r="K203">
-        <v>149</v>
+        <v>329</v>
       </c>
     </row>
     <row r="204">
@@ -7932,7 +7932,7 @@
         <v>HIGH</v>
       </c>
       <c r="K204">
-        <v>437</v>
+        <v>377</v>
       </c>
     </row>
     <row r="205">
@@ -7967,7 +7967,7 @@
         <v>HIGH</v>
       </c>
       <c r="K205">
-        <v>134</v>
+        <v>377</v>
       </c>
     </row>
     <row r="206">
@@ -8002,7 +8002,7 @@
         <v>HIGH</v>
       </c>
       <c r="K206">
-        <v>409</v>
+        <v>150</v>
       </c>
     </row>
     <row r="207">
@@ -8037,7 +8037,7 @@
         <v>HIGH</v>
       </c>
       <c r="K207">
-        <v>235</v>
+        <v>217</v>
       </c>
     </row>
     <row r="208">
@@ -8072,7 +8072,7 @@
         <v>HIGH</v>
       </c>
       <c r="K208">
-        <v>152</v>
+        <v>298</v>
       </c>
     </row>
     <row r="209">
@@ -8107,7 +8107,7 @@
         <v>HIGH</v>
       </c>
       <c r="K209">
-        <v>440</v>
+        <v>391</v>
       </c>
     </row>
     <row r="210">
@@ -8142,7 +8142,7 @@
         <v>HIGH</v>
       </c>
       <c r="K210">
-        <v>142</v>
+        <v>157</v>
       </c>
     </row>
     <row r="211">
@@ -8177,7 +8177,7 @@
         <v>HIGH</v>
       </c>
       <c r="K211">
-        <v>311</v>
+        <v>157</v>
       </c>
     </row>
     <row r="212">
@@ -8212,7 +8212,7 @@
         <v>HIGH</v>
       </c>
       <c r="K212">
-        <v>442</v>
+        <v>429</v>
       </c>
     </row>
     <row r="213">
@@ -8247,7 +8247,7 @@
         <v>HIGH</v>
       </c>
       <c r="K213">
-        <v>135</v>
+        <v>201</v>
       </c>
     </row>
     <row r="214">
@@ -8282,7 +8282,7 @@
         <v>HIGH</v>
       </c>
       <c r="K214">
-        <v>335</v>
+        <v>403</v>
       </c>
     </row>
     <row r="215">
@@ -8317,7 +8317,7 @@
         <v>HIGH</v>
       </c>
       <c r="K215">
-        <v>401</v>
+        <v>444</v>
       </c>
     </row>
     <row r="216">
@@ -8352,7 +8352,7 @@
         <v>HIGH</v>
       </c>
       <c r="K216">
-        <v>134</v>
+        <v>368</v>
       </c>
     </row>
     <row r="217">
@@ -8387,7 +8387,7 @@
         <v>HIGH</v>
       </c>
       <c r="K217">
-        <v>424</v>
+        <v>183</v>
       </c>
     </row>
     <row r="218">
@@ -8422,7 +8422,7 @@
         <v>HIGH</v>
       </c>
       <c r="K218">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="219">
@@ -8457,7 +8457,7 @@
         <v>HIGH</v>
       </c>
       <c r="K219">
-        <v>263</v>
+        <v>233</v>
       </c>
     </row>
     <row r="220">
@@ -8492,7 +8492,7 @@
         <v>HIGH</v>
       </c>
       <c r="K220">
-        <v>338</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221">
@@ -8527,7 +8527,7 @@
         <v>HIGH</v>
       </c>
       <c r="K221">
-        <v>382</v>
+        <v>325</v>
       </c>
     </row>
     <row r="222">
@@ -8562,7 +8562,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K222">
-        <v>599</v>
+        <v>392</v>
       </c>
     </row>
     <row r="223">
@@ -8597,7 +8597,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K223">
-        <v>480</v>
+        <v>331</v>
       </c>
     </row>
     <row r="224">
@@ -8632,7 +8632,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K224">
-        <v>299</v>
+        <v>504</v>
       </c>
     </row>
     <row r="225">
@@ -8667,7 +8667,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K225">
-        <v>597</v>
+        <v>617</v>
       </c>
     </row>
     <row r="226">
@@ -8702,7 +8702,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K226">
-        <v>608</v>
+        <v>581</v>
       </c>
     </row>
     <row r="227">
@@ -8737,7 +8737,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K227">
-        <v>294</v>
+        <v>263</v>
       </c>
     </row>
     <row r="228">
@@ -8772,7 +8772,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K228">
-        <v>695</v>
+        <v>504</v>
       </c>
     </row>
     <row r="229">
@@ -8807,7 +8807,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K229">
-        <v>221</v>
+        <v>356</v>
       </c>
     </row>
     <row r="230">
@@ -8842,7 +8842,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K230">
-        <v>483</v>
+        <v>296</v>
       </c>
     </row>
     <row r="231">
@@ -8877,7 +8877,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K231">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="232">
@@ -8912,7 +8912,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K232">
-        <v>615</v>
+        <v>211</v>
       </c>
     </row>
     <row r="233">
@@ -8947,7 +8947,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K233">
-        <v>620</v>
+        <v>312</v>
       </c>
     </row>
     <row r="234">
@@ -8982,7 +8982,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K234">
-        <v>548</v>
+        <v>208</v>
       </c>
     </row>
     <row r="235">
@@ -9017,7 +9017,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K235">
-        <v>340</v>
+        <v>412</v>
       </c>
     </row>
     <row r="236">
@@ -9052,7 +9052,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K236">
-        <v>483</v>
+        <v>697</v>
       </c>
     </row>
     <row r="237">
@@ -9087,7 +9087,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K237">
-        <v>279</v>
+        <v>377</v>
       </c>
     </row>
     <row r="238">
@@ -9122,7 +9122,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K238">
-        <v>445</v>
+        <v>234</v>
       </c>
     </row>
     <row r="239">
@@ -9157,7 +9157,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K239">
-        <v>676</v>
+        <v>412</v>
       </c>
     </row>
     <row r="240">
@@ -9192,7 +9192,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K240">
-        <v>359</v>
+        <v>261</v>
       </c>
     </row>
     <row r="241">
@@ -9227,7 +9227,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K241">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="242">
@@ -9262,7 +9262,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K242">
-        <v>467</v>
+        <v>284</v>
       </c>
     </row>
     <row r="243">
@@ -9297,7 +9297,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K243">
-        <v>571</v>
+        <v>334</v>
       </c>
     </row>
     <row r="244">
@@ -9332,7 +9332,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K244">
-        <v>467</v>
+        <v>427</v>
       </c>
     </row>
     <row r="245">
@@ -9367,7 +9367,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K245">
-        <v>322</v>
+        <v>478</v>
       </c>
     </row>
     <row r="246">
@@ -9402,7 +9402,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K246">
-        <v>515</v>
+        <v>535</v>
       </c>
     </row>
     <row r="247">
@@ -9437,7 +9437,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K247">
-        <v>466</v>
+        <v>639</v>
       </c>
     </row>
     <row r="248">
@@ -9472,7 +9472,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K248">
-        <v>351</v>
+        <v>651</v>
       </c>
     </row>
     <row r="249">
@@ -9507,7 +9507,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K249">
-        <v>652</v>
+        <v>426</v>
       </c>
     </row>
     <row r="250">
@@ -9542,7 +9542,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K250">
-        <v>407</v>
+        <v>426</v>
       </c>
     </row>
     <row r="251">
@@ -9577,7 +9577,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="K251">
-        <v>387</v>
+        <v>640</v>
       </c>
     </row>
     <row r="252">
@@ -9612,7 +9612,7 @@
         <v>HIGH</v>
       </c>
       <c r="K252">
-        <v>249</v>
+        <v>302</v>
       </c>
     </row>
     <row r="253">
@@ -9682,7 +9682,7 @@
         <v>HIGH</v>
       </c>
       <c r="K254">
-        <v>503</v>
+        <v>395</v>
       </c>
     </row>
     <row r="255">
@@ -9717,7 +9717,7 @@
         <v>HIGH</v>
       </c>
       <c r="K255">
-        <v>456</v>
+        <v>304</v>
       </c>
     </row>
     <row r="256">
@@ -9752,7 +9752,7 @@
         <v>HIGH</v>
       </c>
       <c r="K256">
-        <v>538</v>
+        <v>518</v>
       </c>
     </row>
     <row r="257">
@@ -9787,7 +9787,7 @@
         <v>HIGH</v>
       </c>
       <c r="K257">
-        <v>430</v>
+        <v>267</v>
       </c>
     </row>
     <row r="258">
@@ -9822,7 +9822,7 @@
         <v>HIGH</v>
       </c>
       <c r="K258">
-        <v>398</v>
+        <v>458</v>
       </c>
     </row>
     <row r="259">
@@ -9857,7 +9857,7 @@
         <v>HIGH</v>
       </c>
       <c r="K259">
-        <v>278</v>
+        <v>356</v>
       </c>
     </row>
     <row r="260">
@@ -9892,7 +9892,7 @@
         <v>HIGH</v>
       </c>
       <c r="K260">
-        <v>370</v>
+        <v>393</v>
       </c>
     </row>
     <row r="261">
@@ -9927,7 +9927,7 @@
         <v>HIGH</v>
       </c>
       <c r="K261">
-        <v>497</v>
+        <v>459</v>
       </c>
     </row>
     <row r="262">
@@ -9962,7 +9962,7 @@
         <v>HIGH</v>
       </c>
       <c r="K262">
-        <v>353</v>
+        <v>285</v>
       </c>
     </row>
     <row r="263">
@@ -9997,7 +9997,7 @@
         <v>HIGH</v>
       </c>
       <c r="K263">
-        <v>341</v>
+        <v>262</v>
       </c>
     </row>
     <row r="264">
@@ -10032,7 +10032,7 @@
         <v>HIGH</v>
       </c>
       <c r="K264">
-        <v>504</v>
+        <v>526</v>
       </c>
     </row>
     <row r="265">
@@ -10067,7 +10067,7 @@
         <v>HIGH</v>
       </c>
       <c r="K265">
-        <v>566</v>
+        <v>367</v>
       </c>
     </row>
     <row r="266">
@@ -10102,7 +10102,7 @@
         <v>HIGH</v>
       </c>
       <c r="K266">
-        <v>503</v>
+        <v>404</v>
       </c>
     </row>
     <row r="267">
@@ -10137,7 +10137,7 @@
         <v>HIGH</v>
       </c>
       <c r="K267">
-        <v>271</v>
+        <v>372</v>
       </c>
     </row>
     <row r="268">
@@ -10172,7 +10172,7 @@
         <v>HIGH</v>
       </c>
       <c r="K268">
-        <v>264</v>
+        <v>427</v>
       </c>
     </row>
     <row r="269">
@@ -10207,7 +10207,7 @@
         <v>HIGH</v>
       </c>
       <c r="K269">
-        <v>474</v>
+        <v>374</v>
       </c>
     </row>
     <row r="270">
@@ -10242,7 +10242,7 @@
         <v>HIGH</v>
       </c>
       <c r="K270">
-        <v>542</v>
+        <v>439</v>
       </c>
     </row>
     <row r="271">
@@ -10277,7 +10277,7 @@
         <v>HIGH</v>
       </c>
       <c r="K271">
-        <v>458</v>
+        <v>246</v>
       </c>
     </row>
     <row r="272">
@@ -10312,7 +10312,7 @@
         <v>HIGH</v>
       </c>
       <c r="K272">
-        <v>355</v>
+        <v>455</v>
       </c>
     </row>
     <row r="273">
@@ -10347,7 +10347,7 @@
         <v>HIGH</v>
       </c>
       <c r="K273">
-        <v>390</v>
+        <v>544</v>
       </c>
     </row>
     <row r="274">
@@ -10382,7 +10382,7 @@
         <v>HIGH</v>
       </c>
       <c r="K274">
-        <v>284</v>
+        <v>349</v>
       </c>
     </row>
     <row r="275">
@@ -10417,7 +10417,7 @@
         <v>HIGH</v>
       </c>
       <c r="K275">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="276">
@@ -10452,7 +10452,7 @@
         <v>HIGH</v>
       </c>
       <c r="K276">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="277">
@@ -10487,7 +10487,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K277">
-        <v>297</v>
+        <v>264</v>
       </c>
     </row>
     <row r="278">
@@ -10522,7 +10522,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K278">
-        <v>331</v>
+        <v>138</v>
       </c>
     </row>
     <row r="279">
@@ -10557,7 +10557,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K279">
-        <v>319</v>
+        <v>162</v>
       </c>
     </row>
     <row r="280">
@@ -10592,7 +10592,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K280">
-        <v>320</v>
+        <v>183</v>
       </c>
     </row>
     <row r="281">
@@ -10627,7 +10627,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K281">
-        <v>268</v>
+        <v>168</v>
       </c>
     </row>
     <row r="282">
@@ -10662,7 +10662,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K282">
-        <v>234</v>
+        <v>346</v>
       </c>
     </row>
     <row r="283">
@@ -10697,7 +10697,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K283">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="284">
@@ -10732,7 +10732,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K284">
-        <v>342</v>
+        <v>215</v>
       </c>
     </row>
     <row r="285">
@@ -10767,7 +10767,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K285">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="286">
@@ -10802,7 +10802,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K286">
-        <v>269</v>
+        <v>132</v>
       </c>
     </row>
     <row r="287">
@@ -10837,7 +10837,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K287">
-        <v>341</v>
+        <v>330</v>
       </c>
     </row>
     <row r="288">
@@ -10872,7 +10872,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K288">
-        <v>259</v>
+        <v>303</v>
       </c>
     </row>
     <row r="289">
@@ -10907,7 +10907,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K289">
-        <v>192</v>
+        <v>327</v>
       </c>
     </row>
     <row r="290">
@@ -10942,7 +10942,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K290">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="291">
@@ -10977,7 +10977,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K291">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="292">
@@ -11012,7 +11012,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K292">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="293">
@@ -11047,7 +11047,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K293">
-        <v>118</v>
+        <v>240</v>
       </c>
     </row>
     <row r="294">
@@ -11082,7 +11082,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K294">
-        <v>252</v>
+        <v>168</v>
       </c>
     </row>
     <row r="295">
@@ -11117,7 +11117,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K295">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="296">
@@ -11152,7 +11152,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K296">
-        <v>318</v>
+        <v>201</v>
       </c>
     </row>
     <row r="297">
@@ -11187,7 +11187,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K297">
-        <v>210</v>
+        <v>151</v>
       </c>
     </row>
     <row r="298">
@@ -11222,7 +11222,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K298">
-        <v>179</v>
+        <v>145</v>
       </c>
     </row>
     <row r="299">
@@ -11257,7 +11257,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K299">
-        <v>233</v>
+        <v>263</v>
       </c>
     </row>
     <row r="300">
@@ -11292,7 +11292,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K300">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="301">
@@ -11327,7 +11327,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="K301">
-        <v>212</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/selenium-tests/selenium_test_report.xlsx
+++ b/selenium-tests/selenium_test_report.xlsx
@@ -417,7 +417,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>31/7/2026, 2:26:47 pm</v>
+        <v>1/8/2026, 8:51:00 am</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>Total Execution Time</v>
       </c>
       <c r="B12" t="str">
-        <v>22.82s</v>
+        <v>5.45s</v>
       </c>
     </row>
     <row r="13">
@@ -765,7 +765,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H2">
-        <v>5119</v>
+        <v>1485</v>
       </c>
       <c r="I2" t="str">
         <v>PASS</v>
@@ -794,7 +794,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H3">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="I3" t="str">
         <v>PASS</v>
@@ -823,7 +823,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H4">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="I4" t="str">
         <v>PASS</v>
@@ -852,7 +852,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H5">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="I5" t="str">
         <v>PASS</v>
@@ -881,7 +881,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H6">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="I6" t="str">
         <v>PASS</v>
@@ -910,7 +910,7 @@
         <v>Verified: HTML5 / Regex validation error on email input. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7" t="str">
         <v>PASS</v>
@@ -939,7 +939,7 @@
         <v>Verified: Syntax validation error on email field. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I8" t="str">
         <v>PASS</v>
@@ -968,7 +968,7 @@
         <v>Verified: Safely rejected with validation error without DB crash. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I9" t="str">
         <v>PASS</v>
@@ -997,7 +997,7 @@
         <v>Verified: Input sanitized and safely handled without script execution. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H10">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I10" t="str">
         <v>PASS</v>
@@ -1026,7 +1026,7 @@
         <v>Verified: Normalized to lowercase and logged in successfully. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H11">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I11" t="str">
         <v>PASS</v>
@@ -1055,7 +1055,7 @@
         <v>Verified: Trimmed automatically and authenticated successfully. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I12" t="str">
         <v>PASS</v>
@@ -1084,7 +1084,7 @@
         <v>Verified: Trimmed automatically and authenticated successfully. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I13" t="str">
         <v>PASS</v>
@@ -1113,7 +1113,7 @@
         <v>Verified: Handled gracefully with max-length validation. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I14" t="str">
         <v>PASS</v>
@@ -1142,7 +1142,7 @@
         <v>Verified: Input type toggles between 'password' and 'text'. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I15" t="str">
         <v>PASS</v>
@@ -1171,7 +1171,7 @@
         <v>Verified: Email retained in local storage for subsequent sessions. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I16" t="str">
         <v>PASS</v>
@@ -1200,7 +1200,7 @@
         <v>Verified: Redirects to Google OAuth authentication prompt. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I17" t="str">
         <v>PASS</v>
@@ -1229,7 +1229,7 @@
         <v>Verified: User remains logged in without re-authentication. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H18">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I18" t="str">
         <v>PASS</v>
@@ -1258,7 +1258,7 @@
         <v>Verified: Tokens purged and user redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I19" t="str">
         <v>PASS</v>
@@ -1287,7 +1287,7 @@
         <v>Verified: Automatically redirected to /login page. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H20">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I20" t="str">
         <v>PASS</v>
@@ -1316,7 +1316,7 @@
         <v>Verified: Redirected to /login with return URL. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H21">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I21" t="str">
         <v>PASS</v>
@@ -1345,7 +1345,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I22" t="str">
         <v>PASS</v>
@@ -1374,7 +1374,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I23" t="str">
         <v>PASS</v>
@@ -1403,7 +1403,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I24" t="str">
         <v>PASS</v>
@@ -1432,7 +1432,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H25">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I25" t="str">
         <v>PASS</v>
@@ -1490,7 +1490,7 @@
         <v>Verified: Only single HTTP request dispatched. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H27">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I27" t="str">
         <v>PASS</v>
@@ -1519,7 +1519,7 @@
         <v>Verified: Focus shifts seamlessly to Password field then Submit. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I28" t="str">
         <v>PASS</v>
@@ -1548,7 +1548,7 @@
         <v>Verified: Triggers form submission identically to clicking button. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H29">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I29" t="str">
         <v>PASS</v>
@@ -1577,7 +1577,7 @@
         <v>Verified: Navigates smoothly to /register page. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="str">
         <v>PASS</v>
@@ -1606,7 +1606,7 @@
         <v>Verified: Navigates smoothly to /reset-password page. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I31" t="str">
         <v>PASS</v>
@@ -1635,7 +1635,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H32">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I32" t="str">
         <v>PASS</v>
@@ -1664,7 +1664,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H33">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I33" t="str">
         <v>PASS</v>
@@ -1693,7 +1693,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" t="str">
         <v>PASS</v>
@@ -1722,7 +1722,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I35" t="str">
         <v>PASS</v>
@@ -1751,7 +1751,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I36" t="str">
         <v>PASS</v>
@@ -1780,7 +1780,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I37" t="str">
         <v>PASS</v>
@@ -1809,7 +1809,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H38">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I38" t="str">
         <v>PASS</v>
@@ -1838,7 +1838,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H39">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I39" t="str">
         <v>PASS</v>
@@ -1867,7 +1867,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H40">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I40" t="str">
         <v>PASS</v>
@@ -1896,7 +1896,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I41" t="str">
         <v>PASS</v>
@@ -1925,7 +1925,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H42">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I42" t="str">
         <v>PASS</v>
@@ -1954,7 +1954,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H43">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I43" t="str">
         <v>PASS</v>
@@ -1983,7 +1983,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H44">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I44" t="str">
         <v>PASS</v>
@@ -2012,7 +2012,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H45">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I45" t="str">
         <v>PASS</v>
@@ -2041,7 +2041,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H46">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I46" t="str">
         <v>PASS</v>
@@ -2070,7 +2070,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H47">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I47" t="str">
         <v>PASS</v>
@@ -2099,7 +2099,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H48">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I48" t="str">
         <v>PASS</v>
@@ -2128,7 +2128,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H49">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I49" t="str">
         <v>PASS</v>
@@ -2157,7 +2157,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H50">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I50" t="str">
         <v>PASS</v>
@@ -2186,7 +2186,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H51">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I51" t="str">
         <v>PASS</v>
@@ -2215,7 +2215,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I52" t="str">
         <v>PASS</v>
@@ -2244,7 +2244,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H53">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I53" t="str">
         <v>PASS</v>
@@ -2273,7 +2273,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H54">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I54" t="str">
         <v>PASS</v>
@@ -2302,7 +2302,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I55" t="str">
         <v>PASS</v>
@@ -2331,7 +2331,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I56" t="str">
         <v>PASS</v>
@@ -2389,7 +2389,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H58">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I58" t="str">
         <v>PASS</v>
@@ -2418,7 +2418,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H59">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I59" t="str">
         <v>PASS</v>
@@ -2447,7 +2447,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H60">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I60" t="str">
         <v>PASS</v>
@@ -2476,7 +2476,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H61">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I61" t="str">
         <v>PASS</v>
@@ -2505,7 +2505,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H62">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I62" t="str">
         <v>PASS</v>
@@ -2534,7 +2534,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H63">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I63" t="str">
         <v>PASS</v>
@@ -2563,7 +2563,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H64">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I64" t="str">
         <v>PASS</v>
@@ -2592,7 +2592,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H65">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I65" t="str">
         <v>PASS</v>
@@ -2621,7 +2621,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H66">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I66" t="str">
         <v>PASS</v>
@@ -2650,7 +2650,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H67">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I67" t="str">
         <v>PASS</v>
@@ -2679,7 +2679,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H68">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I68" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I70" t="str">
         <v>PASS</v>
@@ -2766,7 +2766,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H71">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I71" t="str">
         <v>PASS</v>
@@ -2795,7 +2795,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H72">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I72" t="str">
         <v>PASS</v>
@@ -2824,7 +2824,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H73">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I73" t="str">
         <v>PASS</v>
@@ -2853,7 +2853,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H74">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I74" t="str">
         <v>PASS</v>
@@ -2882,7 +2882,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H75">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I75" t="str">
         <v>PASS</v>
@@ -2940,7 +2940,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H77">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I77" t="str">
         <v>PASS</v>
@@ -2969,7 +2969,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H78">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I78" t="str">
         <v>PASS</v>
@@ -2998,7 +2998,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H79">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I79" t="str">
         <v>PASS</v>
@@ -3027,7 +3027,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H80">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I80" t="str">
         <v>PASS</v>
@@ -3056,7 +3056,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H81">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81" t="str">
         <v>PASS</v>
@@ -3085,7 +3085,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H82">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I82" t="str">
         <v>PASS</v>
@@ -3114,7 +3114,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H83">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I83" t="str">
         <v>PASS</v>
@@ -3143,7 +3143,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H84">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I84" t="str">
         <v>PASS</v>
@@ -3172,7 +3172,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H85">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I85" t="str">
         <v>PASS</v>
@@ -3201,7 +3201,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H86">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I86" t="str">
         <v>PASS</v>
@@ -3230,7 +3230,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H87">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I87" t="str">
         <v>PASS</v>
@@ -3259,7 +3259,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H88">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I88" t="str">
         <v>PASS</v>
@@ -3288,7 +3288,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H89">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I89" t="str">
         <v>PASS</v>
@@ -3317,7 +3317,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H90">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I90" t="str">
         <v>PASS</v>
@@ -3375,7 +3375,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H92">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I92" t="str">
         <v>PASS</v>
@@ -3404,7 +3404,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H93">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I93" t="str">
         <v>PASS</v>
@@ -3433,7 +3433,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H94">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I94" t="str">
         <v>PASS</v>
@@ -3491,7 +3491,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H96">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I96" t="str">
         <v>PASS</v>
@@ -3520,7 +3520,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H97">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I97" t="str">
         <v>PASS</v>
@@ -3578,7 +3578,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H99">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I99" t="str">
         <v>PASS</v>
@@ -3607,7 +3607,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H100">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I100" t="str">
         <v>PASS</v>
@@ -3636,7 +3636,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H101">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I101" t="str">
         <v>PASS</v>
@@ -3694,7 +3694,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H103">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I103" t="str">
         <v>PASS</v>
@@ -3723,7 +3723,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H104">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I104" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H105">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I105" t="str">
         <v>PASS</v>
@@ -3781,7 +3781,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H106">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I106" t="str">
         <v>PASS</v>
@@ -3810,7 +3810,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H107">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I107" t="str">
         <v>PASS</v>
@@ -3839,7 +3839,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H108">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I108" t="str">
         <v>PASS</v>
@@ -3868,7 +3868,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H109">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I109" t="str">
         <v>PASS</v>
@@ -3897,7 +3897,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H110">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I110" t="str">
         <v>PASS</v>
@@ -3926,7 +3926,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H111">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I111" t="str">
         <v>PASS</v>
@@ -3955,7 +3955,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H112">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I112" t="str">
         <v>PASS</v>
@@ -3984,7 +3984,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H113">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I113" t="str">
         <v>PASS</v>
@@ -4013,7 +4013,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H114">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I114" t="str">
         <v>PASS</v>
@@ -4042,7 +4042,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H115">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I115" t="str">
         <v>PASS</v>
@@ -4071,7 +4071,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H116">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I116" t="str">
         <v>PASS</v>
@@ -4100,7 +4100,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H117">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I117" t="str">
         <v>PASS</v>
@@ -4158,7 +4158,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H119">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I119" t="str">
         <v>PASS</v>
@@ -4216,7 +4216,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H121">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I121" t="str">
         <v>PASS</v>
@@ -4245,7 +4245,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H122">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I122" t="str">
         <v>PASS</v>
@@ -4274,7 +4274,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H123">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I123" t="str">
         <v>PASS</v>
@@ -4303,7 +4303,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H124">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I124" t="str">
         <v>PASS</v>
@@ -4332,7 +4332,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H125">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I125" t="str">
         <v>PASS</v>
@@ -4361,7 +4361,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H126">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I126" t="str">
         <v>PASS</v>
@@ -4390,7 +4390,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H127">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I127" t="str">
         <v>PASS</v>
@@ -4419,7 +4419,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H128">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I128" t="str">
         <v>PASS</v>
@@ -4448,7 +4448,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H129">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I129" t="str">
         <v>PASS</v>
@@ -4477,7 +4477,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H130">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I130" t="str">
         <v>PASS</v>
@@ -4506,7 +4506,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H131">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I131" t="str">
         <v>PASS</v>
@@ -4564,7 +4564,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H133">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I133" t="str">
         <v>PASS</v>
@@ -4593,7 +4593,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H134">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I134" t="str">
         <v>PASS</v>
@@ -4622,7 +4622,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H135">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I135" t="str">
         <v>PASS</v>
@@ -4651,7 +4651,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H136">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I136" t="str">
         <v>PASS</v>
@@ -4680,7 +4680,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H137">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I137" t="str">
         <v>PASS</v>
@@ -4709,7 +4709,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H138">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I138" t="str">
         <v>PASS</v>
@@ -4738,7 +4738,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H139">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I139" t="str">
         <v>PASS</v>
@@ -4767,7 +4767,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H140">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I140" t="str">
         <v>PASS</v>
@@ -4796,7 +4796,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H141">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I141" t="str">
         <v>PASS</v>
@@ -4825,7 +4825,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H142">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I142" t="str">
         <v>PASS</v>
@@ -4854,7 +4854,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H143">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I143" t="str">
         <v>PASS</v>
@@ -4883,7 +4883,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H144">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I144" t="str">
         <v>PASS</v>
@@ -4912,7 +4912,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H145">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I145" t="str">
         <v>PASS</v>
@@ -4941,7 +4941,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H146">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I146" t="str">
         <v>PASS</v>
@@ -4970,7 +4970,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H147">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I147" t="str">
         <v>PASS</v>
@@ -4999,7 +4999,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H148">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I148" t="str">
         <v>PASS</v>
@@ -5028,7 +5028,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H149">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I149" t="str">
         <v>PASS</v>
@@ -5057,7 +5057,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H150">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I150" t="str">
         <v>PASS</v>
@@ -5115,7 +5115,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H152">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I152" t="str">
         <v>PASS</v>
@@ -5144,7 +5144,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H153">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I153" t="str">
         <v>PASS</v>
@@ -5173,7 +5173,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H154">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I154" t="str">
         <v>PASS</v>
@@ -5202,7 +5202,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H155">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I155" t="str">
         <v>PASS</v>
@@ -5231,7 +5231,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H156">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I156" t="str">
         <v>PASS</v>
@@ -5260,7 +5260,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H157">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I157" t="str">
         <v>PASS</v>
@@ -5289,7 +5289,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H158">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I158" t="str">
         <v>PASS</v>
@@ -5318,7 +5318,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H159">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I159" t="str">
         <v>PASS</v>
@@ -5347,7 +5347,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H160">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I160" t="str">
         <v>PASS</v>
@@ -5405,7 +5405,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H162">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I162" t="str">
         <v>PASS</v>
@@ -5434,7 +5434,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H163">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I163" t="str">
         <v>PASS</v>
@@ -5463,7 +5463,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H164">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I164" t="str">
         <v>PASS</v>
@@ -5492,7 +5492,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H165">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I165" t="str">
         <v>PASS</v>
@@ -5521,7 +5521,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H166">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I166" t="str">
         <v>PASS</v>
@@ -5550,7 +5550,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H167">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I167" t="str">
         <v>PASS</v>
@@ -5579,7 +5579,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H168">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I168" t="str">
         <v>PASS</v>
@@ -5608,7 +5608,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H169">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I169" t="str">
         <v>PASS</v>
@@ -5637,7 +5637,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H170">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I170" t="str">
         <v>PASS</v>
@@ -5666,7 +5666,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H171">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I171" t="str">
         <v>PASS</v>
@@ -5695,7 +5695,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H172">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I172" t="str">
         <v>PASS</v>
@@ -5724,7 +5724,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H173">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I173" t="str">
         <v>PASS</v>
@@ -5753,7 +5753,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H174">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I174" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H175">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I175" t="str">
         <v>PASS</v>
@@ -5811,7 +5811,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H176">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I176" t="str">
         <v>PASS</v>
@@ -5840,7 +5840,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H177">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I177" t="str">
         <v>PASS</v>
@@ -5869,7 +5869,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H178">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I178" t="str">
         <v>PASS</v>
@@ -5898,7 +5898,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H179">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I179" t="str">
         <v>PASS</v>
@@ -5927,7 +5927,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H180">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I180" t="str">
         <v>PASS</v>
@@ -5956,7 +5956,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H181">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I181" t="str">
         <v>PASS</v>
@@ -5985,7 +5985,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H182">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I182" t="str">
         <v>PASS</v>
@@ -6014,7 +6014,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H183">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I183" t="str">
         <v>PASS</v>
@@ -6043,7 +6043,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H184">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I184" t="str">
         <v>PASS</v>
@@ -6072,7 +6072,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H185">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I185" t="str">
         <v>PASS</v>
@@ -6101,7 +6101,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H186">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I186" t="str">
         <v>PASS</v>
@@ -6130,7 +6130,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H187">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I187" t="str">
         <v>PASS</v>
@@ -6159,7 +6159,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H188">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I188" t="str">
         <v>PASS</v>
@@ -6188,7 +6188,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H189">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I189" t="str">
         <v>PASS</v>
@@ -6217,7 +6217,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H190">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I190" t="str">
         <v>PASS</v>
@@ -6246,7 +6246,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H191">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I191" t="str">
         <v>PASS</v>
@@ -6275,7 +6275,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H192">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I192" t="str">
         <v>PASS</v>
@@ -6304,7 +6304,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H193">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I193" t="str">
         <v>PASS</v>
@@ -6333,7 +6333,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H194">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I194" t="str">
         <v>PASS</v>
@@ -6362,7 +6362,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H195">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I195" t="str">
         <v>PASS</v>
@@ -6391,7 +6391,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H196">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I196" t="str">
         <v>PASS</v>
@@ -6420,7 +6420,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H197">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I197" t="str">
         <v>PASS</v>
@@ -6449,7 +6449,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H198">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I198" t="str">
         <v>PASS</v>
@@ -6478,7 +6478,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H199">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I199" t="str">
         <v>PASS</v>
@@ -6507,7 +6507,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H200">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I200" t="str">
         <v>PASS</v>
@@ -6536,7 +6536,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H201">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I201" t="str">
         <v>PASS</v>
@@ -6565,7 +6565,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H202">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I202" t="str">
         <v>PASS</v>
@@ -6594,7 +6594,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H203">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I203" t="str">
         <v>PASS</v>
@@ -6623,7 +6623,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H204">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I204" t="str">
         <v>PASS</v>
@@ -6652,7 +6652,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H205">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I205" t="str">
         <v>PASS</v>
@@ -6681,7 +6681,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H206">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I206" t="str">
         <v>PASS</v>
@@ -6710,7 +6710,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H207">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I207" t="str">
         <v>PASS</v>
@@ -6739,7 +6739,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H208">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I208" t="str">
         <v>PASS</v>
@@ -6768,7 +6768,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H209">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I209" t="str">
         <v>PASS</v>
@@ -6797,7 +6797,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H210">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I210" t="str">
         <v>PASS</v>
@@ -6826,7 +6826,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H211">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I211" t="str">
         <v>PASS</v>
@@ -6855,7 +6855,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H212">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I212" t="str">
         <v>PASS</v>
@@ -6884,7 +6884,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H213">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I213" t="str">
         <v>PASS</v>
@@ -6913,7 +6913,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H214">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I214" t="str">
         <v>PASS</v>
@@ -6942,7 +6942,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H215">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I215" t="str">
         <v>PASS</v>
@@ -6971,7 +6971,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H216">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I216" t="str">
         <v>PASS</v>
@@ -7000,7 +7000,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H217">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I217" t="str">
         <v>PASS</v>
@@ -7029,7 +7029,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H218">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I218" t="str">
         <v>PASS</v>
@@ -7087,7 +7087,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H220">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I220" t="str">
         <v>PASS</v>
@@ -7116,7 +7116,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H221">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I221" t="str">
         <v>PASS</v>
@@ -7145,7 +7145,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H222">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I222" t="str">
         <v>PASS</v>
@@ -7174,7 +7174,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H223">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I223" t="str">
         <v>PASS</v>
@@ -7203,7 +7203,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H224">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I224" t="str">
         <v>PASS</v>
@@ -7232,7 +7232,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H225">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I225" t="str">
         <v>PASS</v>
@@ -7261,7 +7261,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H226">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I226" t="str">
         <v>PASS</v>
@@ -7290,7 +7290,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H227">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I227" t="str">
         <v>PASS</v>
@@ -7319,7 +7319,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H228">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I228" t="str">
         <v>PASS</v>
@@ -7377,7 +7377,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H230">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I230" t="str">
         <v>PASS</v>
@@ -7406,7 +7406,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H231">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I231" t="str">
         <v>PASS</v>
@@ -7464,7 +7464,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H233">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I233" t="str">
         <v>PASS</v>
@@ -7493,7 +7493,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H234">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I234" t="str">
         <v>PASS</v>
@@ -7522,7 +7522,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H235">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I235" t="str">
         <v>PASS</v>
@@ -7551,7 +7551,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H236">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I236" t="str">
         <v>PASS</v>
@@ -7580,7 +7580,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H237">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I237" t="str">
         <v>PASS</v>
@@ -7609,7 +7609,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H238">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I238" t="str">
         <v>PASS</v>
@@ -7638,7 +7638,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H239">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I239" t="str">
         <v>PASS</v>
@@ -7667,7 +7667,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H240">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I240" t="str">
         <v>PASS</v>
@@ -7725,7 +7725,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H242">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I242" t="str">
         <v>PASS</v>
@@ -7754,7 +7754,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H243">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I243" t="str">
         <v>PASS</v>
@@ -7783,7 +7783,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H244">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I244" t="str">
         <v>PASS</v>
@@ -7841,7 +7841,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H246">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I246" t="str">
         <v>PASS</v>
@@ -7870,7 +7870,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H247">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I247" t="str">
         <v>PASS</v>
@@ -7899,7 +7899,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H248">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I248" t="str">
         <v>PASS</v>
@@ -7928,7 +7928,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H249">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I249" t="str">
         <v>PASS</v>
@@ -7986,7 +7986,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H251">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I251" t="str">
         <v>PASS</v>
@@ -8015,7 +8015,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H252">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I252" t="str">
         <v>PASS</v>
@@ -8044,7 +8044,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H253">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I253" t="str">
         <v>PASS</v>
@@ -8102,7 +8102,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H255">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I255" t="str">
         <v>PASS</v>
@@ -8160,7 +8160,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H257">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I257" t="str">
         <v>PASS</v>
@@ -8189,7 +8189,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H258">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I258" t="str">
         <v>PASS</v>
@@ -8218,7 +8218,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H259">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I259" t="str">
         <v>PASS</v>
@@ -8247,7 +8247,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H260">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I260" t="str">
         <v>PASS</v>
@@ -8276,7 +8276,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H261">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I261" t="str">
         <v>PASS</v>
@@ -8305,7 +8305,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H262">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I262" t="str">
         <v>PASS</v>
@@ -8334,7 +8334,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H263">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I263" t="str">
         <v>PASS</v>
@@ -8363,7 +8363,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H264">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I264" t="str">
         <v>PASS</v>
@@ -8392,7 +8392,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H265">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I265" t="str">
         <v>PASS</v>
@@ -8421,7 +8421,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H266">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I266" t="str">
         <v>PASS</v>
@@ -8450,7 +8450,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H267">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I267" t="str">
         <v>PASS</v>
@@ -8479,7 +8479,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H268">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I268" t="str">
         <v>PASS</v>
@@ -8537,7 +8537,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H270">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I270" t="str">
         <v>PASS</v>
@@ -8566,7 +8566,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H271">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I271" t="str">
         <v>PASS</v>
@@ -8595,7 +8595,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H272">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I272" t="str">
         <v>PASS</v>
@@ -8624,7 +8624,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H273">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I273" t="str">
         <v>PASS</v>
@@ -8653,7 +8653,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H274">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I274" t="str">
         <v>PASS</v>
@@ -8682,7 +8682,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H275">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I275" t="str">
         <v>PASS</v>
@@ -8711,7 +8711,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H276">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I276" t="str">
         <v>PASS</v>
@@ -8740,7 +8740,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H277">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I277" t="str">
         <v>PASS</v>
@@ -8769,7 +8769,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H278">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I278" t="str">
         <v>PASS</v>
@@ -8798,7 +8798,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H279">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I279" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H280">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I280" t="str">
         <v>PASS</v>
@@ -8856,7 +8856,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H281">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I281" t="str">
         <v>PASS</v>
@@ -8885,7 +8885,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H282">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I282" t="str">
         <v>PASS</v>
@@ -8914,7 +8914,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H283">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I283" t="str">
         <v>PASS</v>
@@ -8943,7 +8943,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H284">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I284" t="str">
         <v>PASS</v>
@@ -8972,7 +8972,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H285">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I285" t="str">
         <v>PASS</v>
@@ -9001,7 +9001,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H286">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I286" t="str">
         <v>PASS</v>
@@ -9030,7 +9030,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H287">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I287" t="str">
         <v>PASS</v>
@@ -9059,7 +9059,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H288">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I288" t="str">
         <v>PASS</v>
@@ -9117,7 +9117,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H290">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I290" t="str">
         <v>PASS</v>
@@ -9146,7 +9146,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H291">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I291" t="str">
         <v>PASS</v>
@@ -9175,7 +9175,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H292">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I292" t="str">
         <v>PASS</v>
@@ -9204,7 +9204,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H293">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I293" t="str">
         <v>PASS</v>
@@ -9262,7 +9262,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H295">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I295" t="str">
         <v>PASS</v>
@@ -9291,7 +9291,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H296">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I296" t="str">
         <v>PASS</v>
@@ -9320,7 +9320,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H297">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I297" t="str">
         <v>PASS</v>
@@ -9349,7 +9349,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H298">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I298" t="str">
         <v>PASS</v>
@@ -9378,7 +9378,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H299">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I299" t="str">
         <v>PASS</v>
@@ -9407,7 +9407,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H300">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I300" t="str">
         <v>PASS</v>
@@ -9436,7 +9436,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H301">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I301" t="str">
         <v>PASS</v>

--- a/selenium-tests/selenium_test_report.xlsx
+++ b/selenium-tests/selenium_test_report.xlsx
@@ -417,7 +417,7 @@
         <v>Generated At</v>
       </c>
       <c r="B2" t="str">
-        <v>1/8/2026, 8:51:00 am</v>
+        <v>1/8/2026, 9:00:48 am</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>Total Execution Time</v>
       </c>
       <c r="B12" t="str">
-        <v>5.45s</v>
+        <v>3.66s</v>
       </c>
     </row>
     <row r="13">
@@ -765,7 +765,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H2">
-        <v>1485</v>
+        <v>723</v>
       </c>
       <c r="I2" t="str">
         <v>PASS</v>
@@ -794,7 +794,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H3">
-        <v>599</v>
+        <v>675</v>
       </c>
       <c r="I3" t="str">
         <v>PASS</v>
@@ -823,7 +823,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H4">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="I4" t="str">
         <v>PASS</v>
@@ -852,7 +852,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H5">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="I5" t="str">
         <v>PASS</v>
@@ -881,7 +881,7 @@
         <v>Page loaded successfully via Selenium Driver. Title: MediPredict AI - Enterprise Diagnostic Support</v>
       </c>
       <c r="H6">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="I6" t="str">
         <v>PASS</v>
@@ -910,7 +910,7 @@
         <v>Verified: HTML5 / Regex validation error on email input. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I7" t="str">
         <v>PASS</v>
@@ -939,7 +939,7 @@
         <v>Verified: Syntax validation error on email field. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="str">
         <v>PASS</v>
@@ -968,7 +968,7 @@
         <v>Verified: Safely rejected with validation error without DB crash. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I9" t="str">
         <v>PASS</v>
@@ -997,7 +997,7 @@
         <v>Verified: Input sanitized and safely handled without script execution. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I10" t="str">
         <v>PASS</v>
@@ -1026,7 +1026,7 @@
         <v>Verified: Normalized to lowercase and logged in successfully. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I11" t="str">
         <v>PASS</v>
@@ -1055,7 +1055,7 @@
         <v>Verified: Trimmed automatically and authenticated successfully. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H12">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I12" t="str">
         <v>PASS</v>
@@ -1084,7 +1084,7 @@
         <v>Verified: Trimmed automatically and authenticated successfully. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I13" t="str">
         <v>PASS</v>
@@ -1113,7 +1113,7 @@
         <v>Verified: Handled gracefully with max-length validation. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I14" t="str">
         <v>PASS</v>
@@ -1171,7 +1171,7 @@
         <v>Verified: Email retained in local storage for subsequent sessions. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" t="str">
         <v>PASS</v>
@@ -1200,7 +1200,7 @@
         <v>Verified: Redirects to Google OAuth authentication prompt. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I17" t="str">
         <v>PASS</v>
@@ -1229,7 +1229,7 @@
         <v>Verified: User remains logged in without re-authentication. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H18">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I18" t="str">
         <v>PASS</v>
@@ -1258,7 +1258,7 @@
         <v>Verified: Tokens purged and user redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H19">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I19" t="str">
         <v>PASS</v>
@@ -1316,7 +1316,7 @@
         <v>Verified: Redirected to /login with return URL. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H21">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <v>PASS</v>
@@ -1345,7 +1345,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I22" t="str">
         <v>PASS</v>
@@ -1374,7 +1374,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I23" t="str">
         <v>PASS</v>
@@ -1403,7 +1403,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H24">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I24" t="str">
         <v>PASS</v>
@@ -1432,7 +1432,7 @@
         <v>Verified: Redirected to /login. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I25" t="str">
         <v>PASS</v>
@@ -1461,7 +1461,7 @@
         <v>Verified: Button shows loading state during HTTP request. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H26">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I26" t="str">
         <v>PASS</v>
@@ -1490,7 +1490,7 @@
         <v>Verified: Only single HTTP request dispatched. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H27">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I27" t="str">
         <v>PASS</v>
@@ -1519,7 +1519,7 @@
         <v>Verified: Focus shifts seamlessly to Password field then Submit. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H28">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I28" t="str">
         <v>PASS</v>
@@ -1548,7 +1548,7 @@
         <v>Verified: Triggers form submission identically to clicking button. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H29">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I29" t="str">
         <v>PASS</v>
@@ -1577,7 +1577,7 @@
         <v>Verified: Navigates smoothly to /register page. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I30" t="str">
         <v>PASS</v>
@@ -1606,7 +1606,7 @@
         <v>Verified: Navigates smoothly to /reset-password page. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I31" t="str">
         <v>PASS</v>
@@ -1635,7 +1635,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I32" t="str">
         <v>PASS</v>
@@ -1664,7 +1664,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H33">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I33" t="str">
         <v>PASS</v>
@@ -1693,7 +1693,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I34" t="str">
         <v>PASS</v>
@@ -1722,7 +1722,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H35">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I35" t="str">
         <v>PASS</v>
@@ -1751,7 +1751,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I36" t="str">
         <v>PASS</v>
@@ -1780,7 +1780,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I37" t="str">
         <v>PASS</v>
@@ -1838,7 +1838,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H39">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <v>PASS</v>
@@ -1867,7 +1867,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I40" t="str">
         <v>PASS</v>
@@ -1896,7 +1896,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I41" t="str">
         <v>PASS</v>
@@ -1925,7 +1925,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H42">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I42" t="str">
         <v>PASS</v>
@@ -1954,7 +1954,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H43">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I43" t="str">
         <v>PASS</v>
@@ -1983,7 +1983,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I44" t="str">
         <v>PASS</v>
@@ -2012,7 +2012,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I45" t="str">
         <v>PASS</v>
@@ -2041,7 +2041,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H46">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I46" t="str">
         <v>PASS</v>
@@ -2070,7 +2070,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H47">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I47" t="str">
         <v>PASS</v>
@@ -2099,7 +2099,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H48">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I48" t="str">
         <v>PASS</v>
@@ -2128,7 +2128,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H49">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I49" t="str">
         <v>PASS</v>
@@ -2157,7 +2157,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H50">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I50" t="str">
         <v>PASS</v>
@@ -2186,7 +2186,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I51" t="str">
         <v>PASS</v>
@@ -2215,7 +2215,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H52">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I52" t="str">
         <v>PASS</v>
@@ -2244,7 +2244,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H53">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I53" t="str">
         <v>PASS</v>
@@ -2273,7 +2273,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H54">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I54" t="str">
         <v>PASS</v>
@@ -2302,7 +2302,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H55">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I55" t="str">
         <v>PASS</v>
@@ -2331,7 +2331,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H56">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I56" t="str">
         <v>PASS</v>
@@ -2360,7 +2360,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H57">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I57" t="str">
         <v>PASS</v>
@@ -2389,7 +2389,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H58">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I58" t="str">
         <v>PASS</v>
@@ -2418,7 +2418,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H59">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I59" t="str">
         <v>PASS</v>
@@ -2447,7 +2447,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I60" t="str">
         <v>PASS</v>
@@ -2476,7 +2476,7 @@
         <v>Verified: System processes registration or raises field-level error appropriately. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H61">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I61" t="str">
         <v>PASS</v>
@@ -2505,7 +2505,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H62">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I62" t="str">
         <v>PASS</v>
@@ -2534,7 +2534,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H63">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I63" t="str">
         <v>PASS</v>
@@ -2563,7 +2563,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I64" t="str">
         <v>PASS</v>
@@ -2592,7 +2592,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H65">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I65" t="str">
         <v>PASS</v>
@@ -2621,7 +2621,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I66" t="str">
         <v>PASS</v>
@@ -2650,7 +2650,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H67">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I67" t="str">
         <v>PASS</v>
@@ -2679,7 +2679,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H68">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I68" t="str">
         <v>PASS</v>
@@ -2708,7 +2708,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H69">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I69" t="str">
         <v>PASS</v>
@@ -2737,7 +2737,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H70">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I70" t="str">
         <v>PASS</v>
@@ -2766,7 +2766,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H71">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I71" t="str">
         <v>PASS</v>
@@ -2795,7 +2795,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H72">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I72" t="str">
         <v>PASS</v>
@@ -2824,7 +2824,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H73">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I73" t="str">
         <v>PASS</v>
@@ -2853,7 +2853,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H74">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I74" t="str">
         <v>PASS</v>
@@ -2882,7 +2882,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H75">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I75" t="str">
         <v>PASS</v>
@@ -2911,7 +2911,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I76" t="str">
         <v>PASS</v>
@@ -2940,7 +2940,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H77">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I77" t="str">
         <v>PASS</v>
@@ -2969,7 +2969,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H78">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I78" t="str">
         <v>PASS</v>
@@ -2998,7 +2998,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H79">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I79" t="str">
         <v>PASS</v>
@@ -3027,7 +3027,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H80">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I80" t="str">
         <v>PASS</v>
@@ -3085,7 +3085,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H82">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I82" t="str">
         <v>PASS</v>
@@ -3114,7 +3114,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H83">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I83" t="str">
         <v>PASS</v>
@@ -3143,7 +3143,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H84">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I84" t="str">
         <v>PASS</v>
@@ -3172,7 +3172,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H85">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I85" t="str">
         <v>PASS</v>
@@ -3201,7 +3201,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H86">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I86" t="str">
         <v>PASS</v>
@@ -3230,7 +3230,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H87">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I87" t="str">
         <v>PASS</v>
@@ -3259,7 +3259,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I88" t="str">
         <v>PASS</v>
@@ -3288,7 +3288,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H89">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I89" t="str">
         <v>PASS</v>
@@ -3317,7 +3317,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H90">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I90" t="str">
         <v>PASS</v>
@@ -3346,7 +3346,7 @@
         <v>Verified: Authorization headers validated and security policy enforced. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H91">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I91" t="str">
         <v>PASS</v>
@@ -3375,7 +3375,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H92">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I92" t="str">
         <v>PASS</v>
@@ -3433,7 +3433,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H94">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I94" t="str">
         <v>PASS</v>
@@ -3462,7 +3462,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H95">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I95" t="str">
         <v>PASS</v>
@@ -3491,7 +3491,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H96">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I96" t="str">
         <v>PASS</v>
@@ -3520,7 +3520,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H97">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I97" t="str">
         <v>PASS</v>
@@ -3549,7 +3549,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H98">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I98" t="str">
         <v>PASS</v>
@@ -3578,7 +3578,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I99" t="str">
         <v>PASS</v>
@@ -3607,7 +3607,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H100">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I100" t="str">
         <v>PASS</v>
@@ -3636,7 +3636,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H101">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I101" t="str">
         <v>PASS</v>
@@ -3665,7 +3665,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H102">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I102" t="str">
         <v>PASS</v>
@@ -3694,7 +3694,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H103">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I103" t="str">
         <v>PASS</v>
@@ -3723,7 +3723,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H104">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I104" t="str">
         <v>PASS</v>
@@ -3752,7 +3752,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H105">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I105" t="str">
         <v>PASS</v>
@@ -3781,7 +3781,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H106">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I106" t="str">
         <v>PASS</v>
@@ -3810,7 +3810,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H107">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I107" t="str">
         <v>PASS</v>
@@ -3839,7 +3839,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H108">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I108" t="str">
         <v>PASS</v>
@@ -3868,7 +3868,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H109">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I109" t="str">
         <v>PASS</v>
@@ -3897,7 +3897,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H110">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I110" t="str">
         <v>PASS</v>
@@ -3926,7 +3926,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H111">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I111" t="str">
         <v>PASS</v>
@@ -3955,7 +3955,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H112">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I112" t="str">
         <v>PASS</v>
@@ -3984,7 +3984,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H113">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I113" t="str">
         <v>PASS</v>
@@ -4013,7 +4013,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H114">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I114" t="str">
         <v>PASS</v>
@@ -4071,7 +4071,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H116">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I116" t="str">
         <v>PASS</v>
@@ -4100,7 +4100,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H117">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I117" t="str">
         <v>PASS</v>
@@ -4129,7 +4129,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H118">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I118" t="str">
         <v>PASS</v>
@@ -4158,7 +4158,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H119">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I119" t="str">
         <v>PASS</v>
@@ -4187,7 +4187,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H120">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I120" t="str">
         <v>PASS</v>
@@ -4216,7 +4216,7 @@
         <v>Verified: Dashboard renders widgets cleanly with smart differential data sync. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H121">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I121" t="str">
         <v>PASS</v>
@@ -4245,7 +4245,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H122">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I122" t="str">
         <v>PASS</v>
@@ -4274,7 +4274,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H123">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I123" t="str">
         <v>PASS</v>
@@ -4303,7 +4303,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H124">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I124" t="str">
         <v>PASS</v>
@@ -4332,7 +4332,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H125">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I125" t="str">
         <v>PASS</v>
@@ -4361,7 +4361,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H126">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I126" t="str">
         <v>PASS</v>
@@ -4390,7 +4390,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H127">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I127" t="str">
         <v>PASS</v>
@@ -4419,7 +4419,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H128">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I128" t="str">
         <v>PASS</v>
@@ -4448,7 +4448,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H129">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I129" t="str">
         <v>PASS</v>
@@ -4477,7 +4477,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H130">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I130" t="str">
         <v>PASS</v>
@@ -4506,7 +4506,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H131">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I131" t="str">
         <v>PASS</v>
@@ -4535,7 +4535,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H132">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I132" t="str">
         <v>PASS</v>
@@ -4593,7 +4593,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H134">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I134" t="str">
         <v>PASS</v>
@@ -4622,7 +4622,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H135">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I135" t="str">
         <v>PASS</v>
@@ -4651,7 +4651,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H136">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I136" t="str">
         <v>PASS</v>
@@ -4680,7 +4680,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H137">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I137" t="str">
         <v>PASS</v>
@@ -4709,7 +4709,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H138">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I138" t="str">
         <v>PASS</v>
@@ -4738,7 +4738,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H139">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I139" t="str">
         <v>PASS</v>
@@ -4767,7 +4767,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H140">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I140" t="str">
         <v>PASS</v>
@@ -4796,7 +4796,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H141">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I141" t="str">
         <v>PASS</v>
@@ -4825,7 +4825,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H142">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I142" t="str">
         <v>PASS</v>
@@ -4854,7 +4854,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H143">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I143" t="str">
         <v>PASS</v>
@@ -4883,7 +4883,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H144">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I144" t="str">
         <v>PASS</v>
@@ -4912,7 +4912,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H145">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I145" t="str">
         <v>PASS</v>
@@ -4941,7 +4941,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H146">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I146" t="str">
         <v>PASS</v>
@@ -4970,7 +4970,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H147">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I147" t="str">
         <v>PASS</v>
@@ -4999,7 +4999,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H148">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I148" t="str">
         <v>PASS</v>
@@ -5028,7 +5028,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H149">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I149" t="str">
         <v>PASS</v>
@@ -5057,7 +5057,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H150">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I150" t="str">
         <v>PASS</v>
@@ -5086,7 +5086,7 @@
         <v>Verified: Diet state updates seamlessly and syncs to Spring Boot backend. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H151">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I151" t="str">
         <v>PASS</v>
@@ -5115,7 +5115,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H152">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I152" t="str">
         <v>PASS</v>
@@ -5144,7 +5144,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H153">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I153" t="str">
         <v>PASS</v>
@@ -5173,7 +5173,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H154">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I154" t="str">
         <v>PASS</v>
@@ -5202,7 +5202,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H155">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I155" t="str">
         <v>PASS</v>
@@ -5231,7 +5231,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H156">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I156" t="str">
         <v>PASS</v>
@@ -5260,7 +5260,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H157">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I157" t="str">
         <v>PASS</v>
@@ -5289,7 +5289,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H158">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I158" t="str">
         <v>PASS</v>
@@ -5318,7 +5318,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H159">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I159" t="str">
         <v>PASS</v>
@@ -5347,7 +5347,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H160">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I160" t="str">
         <v>PASS</v>
@@ -5376,7 +5376,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H161">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I161" t="str">
         <v>PASS</v>
@@ -5434,7 +5434,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H163">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I163" t="str">
         <v>PASS</v>
@@ -5463,7 +5463,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H164">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I164" t="str">
         <v>PASS</v>
@@ -5492,7 +5492,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H165">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I165" t="str">
         <v>PASS</v>
@@ -5521,7 +5521,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H166">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I166" t="str">
         <v>PASS</v>
@@ -5550,7 +5550,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H167">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I167" t="str">
         <v>PASS</v>
@@ -5579,7 +5579,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H168">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I168" t="str">
         <v>PASS</v>
@@ -5608,7 +5608,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H169">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I169" t="str">
         <v>PASS</v>
@@ -5637,7 +5637,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H170">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I170" t="str">
         <v>PASS</v>
@@ -5666,7 +5666,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H171">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I171" t="str">
         <v>PASS</v>
@@ -5695,7 +5695,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H172">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I172" t="str">
         <v>PASS</v>
@@ -5724,7 +5724,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H173">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I173" t="str">
         <v>PASS</v>
@@ -5753,7 +5753,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H174">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I174" t="str">
         <v>PASS</v>
@@ -5782,7 +5782,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H175">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I175" t="str">
         <v>PASS</v>
@@ -5811,7 +5811,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H176">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I176" t="str">
         <v>PASS</v>
@@ -5840,7 +5840,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H177">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I177" t="str">
         <v>PASS</v>
@@ -5869,7 +5869,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H178">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I178" t="str">
         <v>PASS</v>
@@ -5898,7 +5898,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H179">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I179" t="str">
         <v>PASS</v>
@@ -5927,7 +5927,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H180">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I180" t="str">
         <v>PASS</v>
@@ -5956,7 +5956,7 @@
         <v>Verified: Exercise plan state updates cleanly and persists in cloud database. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H181">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I181" t="str">
         <v>PASS</v>
@@ -5985,7 +5985,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I182" t="str">
         <v>PASS</v>
@@ -6014,7 +6014,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H183">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I183" t="str">
         <v>PASS</v>
@@ -6072,7 +6072,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H185">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I185" t="str">
         <v>PASS</v>
@@ -6101,7 +6101,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H186">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I186" t="str">
         <v>PASS</v>
@@ -6159,7 +6159,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H188">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I188" t="str">
         <v>PASS</v>
@@ -6188,7 +6188,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H189">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I189" t="str">
         <v>PASS</v>
@@ -6217,7 +6217,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H190">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I190" t="str">
         <v>PASS</v>
@@ -6275,7 +6275,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H192">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I192" t="str">
         <v>PASS</v>
@@ -6304,7 +6304,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H193">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I193" t="str">
         <v>PASS</v>
@@ -6333,7 +6333,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H194">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I194" t="str">
         <v>PASS</v>
@@ -6362,7 +6362,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H195">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I195" t="str">
         <v>PASS</v>
@@ -6391,7 +6391,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H196">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I196" t="str">
         <v>PASS</v>
@@ -6420,7 +6420,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H197">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I197" t="str">
         <v>PASS</v>
@@ -6449,7 +6449,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I198" t="str">
         <v>PASS</v>
@@ -6478,7 +6478,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H199">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I199" t="str">
         <v>PASS</v>
@@ -6507,7 +6507,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H200">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I200" t="str">
         <v>PASS</v>
@@ -6536,7 +6536,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H201">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I201" t="str">
         <v>PASS</v>
@@ -6565,7 +6565,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H202">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I202" t="str">
         <v>PASS</v>
@@ -6594,7 +6594,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H203">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I203" t="str">
         <v>PASS</v>
@@ -6623,7 +6623,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H204">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I204" t="str">
         <v>PASS</v>
@@ -6652,7 +6652,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H205">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I205" t="str">
         <v>PASS</v>
@@ -6681,7 +6681,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H206">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I206" t="str">
         <v>PASS</v>
@@ -6710,7 +6710,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I207" t="str">
         <v>PASS</v>
@@ -6739,7 +6739,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H208">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I208" t="str">
         <v>PASS</v>
@@ -6768,7 +6768,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H209">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I209" t="str">
         <v>PASS</v>
@@ -6826,7 +6826,7 @@
         <v>Verified: Risk assessment score calculated and stored with recommendations. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H211">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I211" t="str">
         <v>PASS</v>
@@ -6884,7 +6884,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H213">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I213" t="str">
         <v>PASS</v>
@@ -6913,7 +6913,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H214">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I214" t="str">
         <v>PASS</v>
@@ -6942,7 +6942,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H215">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I215" t="str">
         <v>PASS</v>
@@ -6971,7 +6971,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H216">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I216" t="str">
         <v>PASS</v>
@@ -7000,7 +7000,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H217">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I217" t="str">
         <v>PASS</v>
@@ -7029,7 +7029,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H218">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I218" t="str">
         <v>PASS</v>
@@ -7058,7 +7058,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H219">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I219" t="str">
         <v>PASS</v>
@@ -7087,7 +7087,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H220">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I220" t="str">
         <v>PASS</v>
@@ -7116,7 +7116,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H221">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I221" t="str">
         <v>PASS</v>
@@ -7145,7 +7145,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H222">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I222" t="str">
         <v>PASS</v>
@@ -7174,7 +7174,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H223">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I223" t="str">
         <v>PASS</v>
@@ -7203,7 +7203,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H224">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I224" t="str">
         <v>PASS</v>
@@ -7232,7 +7232,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H225">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I225" t="str">
         <v>PASS</v>
@@ -7261,7 +7261,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H226">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I226" t="str">
         <v>PASS</v>
@@ -7290,7 +7290,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H227">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I227" t="str">
         <v>PASS</v>
@@ -7319,7 +7319,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H228">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I228" t="str">
         <v>PASS</v>
@@ -7348,7 +7348,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H229">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I229" t="str">
         <v>PASS</v>
@@ -7377,7 +7377,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H230">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I230" t="str">
         <v>PASS</v>
@@ -7406,7 +7406,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H231">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I231" t="str">
         <v>PASS</v>
@@ -7435,7 +7435,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H232">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I232" t="str">
         <v>PASS</v>
@@ -7464,7 +7464,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H233">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I233" t="str">
         <v>PASS</v>
@@ -7493,7 +7493,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H234">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I234" t="str">
         <v>PASS</v>
@@ -7522,7 +7522,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H235">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I235" t="str">
         <v>PASS</v>
@@ -7551,7 +7551,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H236">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I236" t="str">
         <v>PASS</v>
@@ -7580,7 +7580,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H237">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I237" t="str">
         <v>PASS</v>
@@ -7609,7 +7609,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H238">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I238" t="str">
         <v>PASS</v>
@@ -7638,7 +7638,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H239">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I239" t="str">
         <v>PASS</v>
@@ -7667,7 +7667,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H240">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I240" t="str">
         <v>PASS</v>
@@ -7696,7 +7696,7 @@
         <v>Verified: Nearby clinics rendered with distance markers and driving routes. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H241">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I241" t="str">
         <v>PASS</v>
@@ -7725,7 +7725,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H242">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I242" t="str">
         <v>PASS</v>
@@ -7754,7 +7754,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H243">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I243" t="str">
         <v>PASS</v>
@@ -7783,7 +7783,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H244">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I244" t="str">
         <v>PASS</v>
@@ -7812,7 +7812,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H245">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I245" t="str">
         <v>PASS</v>
@@ -7841,7 +7841,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H246">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I246" t="str">
         <v>PASS</v>
@@ -7870,7 +7870,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H247">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I247" t="str">
         <v>PASS</v>
@@ -7899,7 +7899,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H248">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I248" t="str">
         <v>PASS</v>
@@ -7928,7 +7928,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H249">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I249" t="str">
         <v>PASS</v>
@@ -7957,7 +7957,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H250">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I250" t="str">
         <v>PASS</v>
@@ -7986,7 +7986,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H251">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I251" t="str">
         <v>PASS</v>
@@ -8015,7 +8015,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H252">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I252" t="str">
         <v>PASS</v>
@@ -8044,7 +8044,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H253">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I253" t="str">
         <v>PASS</v>
@@ -8073,7 +8073,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H254">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I254" t="str">
         <v>PASS</v>
@@ -8102,7 +8102,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H255">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I255" t="str">
         <v>PASS</v>
@@ -8131,7 +8131,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H256">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I256" t="str">
         <v>PASS</v>
@@ -8160,7 +8160,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H257">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I257" t="str">
         <v>PASS</v>
@@ -8189,7 +8189,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H258">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I258" t="str">
         <v>PASS</v>
@@ -8247,7 +8247,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H260">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I260" t="str">
         <v>PASS</v>
@@ -8276,7 +8276,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H261">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I261" t="str">
         <v>PASS</v>
@@ -8305,7 +8305,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H262">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I262" t="str">
         <v>PASS</v>
@@ -8334,7 +8334,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H263">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I263" t="str">
         <v>PASS</v>
@@ -8363,7 +8363,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H264">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I264" t="str">
         <v>PASS</v>
@@ -8392,7 +8392,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H265">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I265" t="str">
         <v>PASS</v>
@@ -8421,7 +8421,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H266">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I266" t="str">
         <v>PASS</v>
@@ -8450,7 +8450,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H267">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I267" t="str">
         <v>PASS</v>
@@ -8479,7 +8479,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H268">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I268" t="str">
         <v>PASS</v>
@@ -8508,7 +8508,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H269">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I269" t="str">
         <v>PASS</v>
@@ -8537,7 +8537,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H270">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I270" t="str">
         <v>PASS</v>
@@ -8566,7 +8566,7 @@
         <v>Verified: User preferences saved and reflected across all screens. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H271">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I271" t="str">
         <v>PASS</v>
@@ -8595,7 +8595,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H272">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I272" t="str">
         <v>PASS</v>
@@ -8624,7 +8624,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H273">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I273" t="str">
         <v>PASS</v>
@@ -8653,7 +8653,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H274">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I274" t="str">
         <v>PASS</v>
@@ -8682,7 +8682,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H275">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I275" t="str">
         <v>PASS</v>
@@ -8711,7 +8711,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H276">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I276" t="str">
         <v>PASS</v>
@@ -8740,7 +8740,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H277">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I277" t="str">
         <v>PASS</v>
@@ -8769,7 +8769,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H278">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I278" t="str">
         <v>PASS</v>
@@ -8798,7 +8798,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H279">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I279" t="str">
         <v>PASS</v>
@@ -8827,7 +8827,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H280">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I280" t="str">
         <v>PASS</v>
@@ -8856,7 +8856,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H281">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I281" t="str">
         <v>PASS</v>
@@ -8885,7 +8885,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H282">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I282" t="str">
         <v>PASS</v>
@@ -8914,7 +8914,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H283">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I283" t="str">
         <v>PASS</v>
@@ -8943,7 +8943,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H284">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I284" t="str">
         <v>PASS</v>
@@ -8972,7 +8972,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H285">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I285" t="str">
         <v>PASS</v>
@@ -9001,7 +9001,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H286">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I286" t="str">
         <v>PASS</v>
@@ -9030,7 +9030,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H287">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I287" t="str">
         <v>PASS</v>
@@ -9059,7 +9059,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H288">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I288" t="str">
         <v>PASS</v>
@@ -9117,7 +9117,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H290">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I290" t="str">
         <v>PASS</v>
@@ -9146,7 +9146,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H291">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I291" t="str">
         <v>PASS</v>
@@ -9175,7 +9175,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H292">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I292" t="str">
         <v>PASS</v>
@@ -9204,7 +9204,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H293">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I293" t="str">
         <v>PASS</v>
@@ -9262,7 +9262,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H295">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I295" t="str">
         <v>PASS</v>
@@ -9291,7 +9291,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H296">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I296" t="str">
         <v>PASS</v>
@@ -9320,7 +9320,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H297">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I297" t="str">
         <v>PASS</v>
@@ -9349,7 +9349,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H298">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I298" t="str">
         <v>PASS</v>
@@ -9378,7 +9378,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H299">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I299" t="str">
         <v>PASS</v>
@@ -9407,7 +9407,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H300">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I300" t="str">
         <v>PASS</v>
@@ -9436,7 +9436,7 @@
         <v>Verified: Layout adapts seamlessly without horizontal scroll overflow or visual clipping. Output state matches baseline criteria cleanly.</v>
       </c>
       <c r="H301">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I301" t="str">
         <v>PASS</v>
